--- a/Projetos/draxos-mobile/docs/economy/generated/draxos_mobile_economy_simulator.xlsx
+++ b/Projetos/draxos-mobile/docs/economy/generated/draxos_mobile_economy_simulator.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Upgrade de varinha e spells</t>
+          <t>Upgrade de Instrumento Ritual e spells</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Upgrade de pets</t>
+          <t>Upgrade de Familiares</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Upgrade de passivas</t>
+          <t>Upgrade de Doutrinas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qualidade e crafting da varinha</t>
+          <t>Qualidade e crafting do Instrumento Ritual</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/Projetos/draxos-mobile/docs/economy/generated/draxos_mobile_economy_simulator.xlsx
+++ b/Projetos/draxos-mobile/docs/economy/generated/draxos_mobile_economy_simulator.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qualidade e crafting do Instrumento Ritual</t>
+          <t>Qualidade, crafting e materia-prima de itens</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>weapon_quality</t>
+          <t>weapon_quality,crafting</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1304,7 +1304,7 @@
         <v>1080</v>
       </c>
       <c r="L2">
-        <v>738</v>
+        <v>73800</v>
       </c>
       <c r="M2">
         <v>15</v>
@@ -1358,7 +1358,7 @@
         <v>1560</v>
       </c>
       <c r="L3">
-        <v>1320</v>
+        <v>132000</v>
       </c>
       <c r="M3">
         <v>30</v>
@@ -1412,7 +1412,7 @@
         <v>2040</v>
       </c>
       <c r="L4">
-        <v>1560</v>
+        <v>156000</v>
       </c>
       <c r="M4">
         <v>90</v>
@@ -1466,7 +1466,7 @@
         <v>3000</v>
       </c>
       <c r="L5">
-        <v>2160</v>
+        <v>216000</v>
       </c>
       <c r="M5">
         <v>90</v>
@@ -1520,7 +1520,7 @@
         <v>3600</v>
       </c>
       <c r="L6">
-        <v>2640</v>
+        <v>264000</v>
       </c>
       <c r="M6">
         <v>90</v>
@@ -1576,7 +1576,7 @@
         <v>1209</v>
       </c>
       <c r="L7">
-        <v>1023</v>
+        <v>102300</v>
       </c>
       <c r="M7">
         <v>15</v>
@@ -1673,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>0.25</v>
@@ -1785,7 +1785,7 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="H6">
         <v>0.5</v>
@@ -1813,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>8</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2036,11 +2036,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30 * cap</t>
+          <t>3000 * cap</t>
         </is>
       </c>
       <c r="D9">
-        <v>1200</v>
+        <v>120000</v>
       </c>
     </row>
   </sheetData>
@@ -2154,7 +2154,7 @@
         <v>9</v>
       </c>
       <c r="J2">
-        <v>6.15</v>
+        <v>615</v>
       </c>
       <c r="K2">
         <v>0.13</v>
@@ -2193,7 +2193,7 @@
         <v>18</v>
       </c>
       <c r="J3">
-        <v>12.3</v>
+        <v>1230</v>
       </c>
       <c r="K3">
         <v>0.25</v>
@@ -2232,7 +2232,7 @@
         <v>27</v>
       </c>
       <c r="J4">
-        <v>18.45</v>
+        <v>1845</v>
       </c>
       <c r="K4">
         <v>0.38</v>
@@ -2271,7 +2271,7 @@
         <v>36</v>
       </c>
       <c r="J5">
-        <v>24.6</v>
+        <v>2460</v>
       </c>
       <c r="K5">
         <v>0.5</v>
@@ -2310,7 +2310,7 @@
         <v>45</v>
       </c>
       <c r="J6">
-        <v>30.75</v>
+        <v>3075</v>
       </c>
       <c r="K6">
         <v>0.63</v>
@@ -2349,7 +2349,7 @@
         <v>54</v>
       </c>
       <c r="J7">
-        <v>36.9</v>
+        <v>3690</v>
       </c>
       <c r="K7">
         <v>0.75</v>
@@ -2388,7 +2388,7 @@
         <v>63</v>
       </c>
       <c r="J8">
-        <v>43.05</v>
+        <v>4305</v>
       </c>
       <c r="K8">
         <v>0.88</v>
@@ -2427,7 +2427,7 @@
         <v>72</v>
       </c>
       <c r="J9">
-        <v>49.2</v>
+        <v>4920</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -2466,7 +2466,7 @@
         <v>81</v>
       </c>
       <c r="J10">
-        <v>55.35</v>
+        <v>5535</v>
       </c>
       <c r="K10">
         <v>1.13</v>
@@ -2505,7 +2505,7 @@
         <v>90</v>
       </c>
       <c r="J11">
-        <v>61.5</v>
+        <v>6150</v>
       </c>
       <c r="K11">
         <v>1.25</v>
@@ -2544,7 +2544,7 @@
         <v>99</v>
       </c>
       <c r="J12">
-        <v>67.65</v>
+        <v>6765</v>
       </c>
       <c r="K12">
         <v>1.38</v>
@@ -2583,7 +2583,7 @@
         <v>108</v>
       </c>
       <c r="J13">
-        <v>73.8</v>
+        <v>7380</v>
       </c>
       <c r="K13">
         <v>1.5</v>
@@ -2622,7 +2622,7 @@
         <v>117</v>
       </c>
       <c r="J14">
-        <v>79.95</v>
+        <v>7995</v>
       </c>
       <c r="K14">
         <v>1.63</v>
@@ -2661,7 +2661,7 @@
         <v>126</v>
       </c>
       <c r="J15">
-        <v>86.1</v>
+        <v>8610</v>
       </c>
       <c r="K15">
         <v>1.75</v>
@@ -2700,7 +2700,7 @@
         <v>135</v>
       </c>
       <c r="J16">
-        <v>92.25</v>
+        <v>9225</v>
       </c>
       <c r="K16">
         <v>1.88</v>
@@ -2739,7 +2739,7 @@
         <v>144</v>
       </c>
       <c r="J17">
-        <v>98.4</v>
+        <v>9840</v>
       </c>
       <c r="K17">
         <v>2</v>
@@ -2778,7 +2778,7 @@
         <v>153</v>
       </c>
       <c r="J18">
-        <v>104.55</v>
+        <v>10455</v>
       </c>
       <c r="K18">
         <v>2.13</v>
@@ -2817,7 +2817,7 @@
         <v>162</v>
       </c>
       <c r="J19">
-        <v>110.7</v>
+        <v>11070</v>
       </c>
       <c r="K19">
         <v>2.25</v>
@@ -2856,7 +2856,7 @@
         <v>171</v>
       </c>
       <c r="J20">
-        <v>116.85</v>
+        <v>11685</v>
       </c>
       <c r="K20">
         <v>2.38</v>
@@ -2895,7 +2895,7 @@
         <v>180</v>
       </c>
       <c r="J21">
-        <v>123</v>
+        <v>12300</v>
       </c>
       <c r="K21">
         <v>2.5</v>
@@ -2934,7 +2934,7 @@
         <v>189</v>
       </c>
       <c r="J22">
-        <v>129.15</v>
+        <v>12915</v>
       </c>
       <c r="K22">
         <v>2.63</v>
@@ -2973,7 +2973,7 @@
         <v>198</v>
       </c>
       <c r="J23">
-        <v>135.3</v>
+        <v>13530</v>
       </c>
       <c r="K23">
         <v>2.75</v>
@@ -3012,7 +3012,7 @@
         <v>207</v>
       </c>
       <c r="J24">
-        <v>141.45</v>
+        <v>14145</v>
       </c>
       <c r="K24">
         <v>2.88</v>
@@ -3051,7 +3051,7 @@
         <v>216</v>
       </c>
       <c r="J25">
-        <v>147.6</v>
+        <v>14760</v>
       </c>
       <c r="K25">
         <v>3</v>
@@ -3090,7 +3090,7 @@
         <v>225</v>
       </c>
       <c r="J26">
-        <v>153.75</v>
+        <v>15375</v>
       </c>
       <c r="K26">
         <v>3.13</v>
@@ -3129,7 +3129,7 @@
         <v>234</v>
       </c>
       <c r="J27">
-        <v>159.9</v>
+        <v>15990</v>
       </c>
       <c r="K27">
         <v>3.25</v>
@@ -3168,7 +3168,7 @@
         <v>243</v>
       </c>
       <c r="J28">
-        <v>166.05</v>
+        <v>16605</v>
       </c>
       <c r="K28">
         <v>3.38</v>
@@ -3207,7 +3207,7 @@
         <v>252</v>
       </c>
       <c r="J29">
-        <v>172.2</v>
+        <v>17220</v>
       </c>
       <c r="K29">
         <v>3.5</v>
@@ -3246,7 +3246,7 @@
         <v>261</v>
       </c>
       <c r="J30">
-        <v>178.35</v>
+        <v>17835</v>
       </c>
       <c r="K30">
         <v>3.63</v>
@@ -3285,7 +3285,7 @@
         <v>270</v>
       </c>
       <c r="J31">
-        <v>184.5</v>
+        <v>18450</v>
       </c>
       <c r="K31">
         <v>3.75</v>
@@ -3324,7 +3324,7 @@
         <v>279</v>
       </c>
       <c r="J32">
-        <v>190.65</v>
+        <v>19065</v>
       </c>
       <c r="K32">
         <v>3.88</v>
@@ -3363,7 +3363,7 @@
         <v>288</v>
       </c>
       <c r="J33">
-        <v>196.8</v>
+        <v>19680</v>
       </c>
       <c r="K33">
         <v>4</v>
@@ -3402,7 +3402,7 @@
         <v>297</v>
       </c>
       <c r="J34">
-        <v>202.95</v>
+        <v>20295</v>
       </c>
       <c r="K34">
         <v>4.13</v>
@@ -3441,7 +3441,7 @@
         <v>306</v>
       </c>
       <c r="J35">
-        <v>209.1</v>
+        <v>20910</v>
       </c>
       <c r="K35">
         <v>4.25</v>
@@ -3480,7 +3480,7 @@
         <v>315</v>
       </c>
       <c r="J36">
-        <v>215.25</v>
+        <v>21525</v>
       </c>
       <c r="K36">
         <v>4.38</v>
@@ -3519,7 +3519,7 @@
         <v>324</v>
       </c>
       <c r="J37">
-        <v>221.4</v>
+        <v>22140</v>
       </c>
       <c r="K37">
         <v>4.5</v>
@@ -3558,7 +3558,7 @@
         <v>333</v>
       </c>
       <c r="J38">
-        <v>227.55</v>
+        <v>22755</v>
       </c>
       <c r="K38">
         <v>4.63</v>
@@ -3597,7 +3597,7 @@
         <v>342</v>
       </c>
       <c r="J39">
-        <v>233.7</v>
+        <v>23370</v>
       </c>
       <c r="K39">
         <v>4.75</v>
@@ -3636,7 +3636,7 @@
         <v>351</v>
       </c>
       <c r="J40">
-        <v>239.85</v>
+        <v>23985</v>
       </c>
       <c r="K40">
         <v>4.88</v>
@@ -3675,7 +3675,7 @@
         <v>360</v>
       </c>
       <c r="J41">
-        <v>246</v>
+        <v>24600</v>
       </c>
       <c r="K41">
         <v>5</v>
@@ -3714,7 +3714,7 @@
         <v>369</v>
       </c>
       <c r="J42">
-        <v>252.15</v>
+        <v>25215</v>
       </c>
       <c r="K42">
         <v>5.13</v>
@@ -3753,7 +3753,7 @@
         <v>378</v>
       </c>
       <c r="J43">
-        <v>258.3</v>
+        <v>25830</v>
       </c>
       <c r="K43">
         <v>5.25</v>
@@ -3792,7 +3792,7 @@
         <v>387</v>
       </c>
       <c r="J44">
-        <v>264.45</v>
+        <v>26445</v>
       </c>
       <c r="K44">
         <v>5.38</v>
@@ -3831,7 +3831,7 @@
         <v>396</v>
       </c>
       <c r="J45">
-        <v>270.6</v>
+        <v>27060</v>
       </c>
       <c r="K45">
         <v>5.5</v>
@@ -3870,7 +3870,7 @@
         <v>405</v>
       </c>
       <c r="J46">
-        <v>276.75</v>
+        <v>27675</v>
       </c>
       <c r="K46">
         <v>5.63</v>
@@ -3909,7 +3909,7 @@
         <v>414</v>
       </c>
       <c r="J47">
-        <v>282.9</v>
+        <v>28290</v>
       </c>
       <c r="K47">
         <v>5.75</v>
@@ -3948,7 +3948,7 @@
         <v>423</v>
       </c>
       <c r="J48">
-        <v>289.05</v>
+        <v>28905</v>
       </c>
       <c r="K48">
         <v>5.88</v>
@@ -3987,7 +3987,7 @@
         <v>432</v>
       </c>
       <c r="J49">
-        <v>295.2</v>
+        <v>29520</v>
       </c>
       <c r="K49">
         <v>6</v>
@@ -4026,7 +4026,7 @@
         <v>441</v>
       </c>
       <c r="J50">
-        <v>301.35</v>
+        <v>30135</v>
       </c>
       <c r="K50">
         <v>6.13</v>
@@ -4065,7 +4065,7 @@
         <v>450</v>
       </c>
       <c r="J51">
-        <v>307.5</v>
+        <v>30750</v>
       </c>
       <c r="K51">
         <v>6.25</v>
@@ -4104,7 +4104,7 @@
         <v>459</v>
       </c>
       <c r="J52">
-        <v>313.65</v>
+        <v>31365</v>
       </c>
       <c r="K52">
         <v>6.38</v>
@@ -4143,7 +4143,7 @@
         <v>468</v>
       </c>
       <c r="J53">
-        <v>319.8</v>
+        <v>31980</v>
       </c>
       <c r="K53">
         <v>6.5</v>
@@ -4182,7 +4182,7 @@
         <v>477</v>
       </c>
       <c r="J54">
-        <v>325.95</v>
+        <v>32595</v>
       </c>
       <c r="K54">
         <v>6.63</v>
@@ -4221,7 +4221,7 @@
         <v>486</v>
       </c>
       <c r="J55">
-        <v>332.1</v>
+        <v>33210</v>
       </c>
       <c r="K55">
         <v>6.75</v>
@@ -4260,7 +4260,7 @@
         <v>495</v>
       </c>
       <c r="J56">
-        <v>338.25</v>
+        <v>33825</v>
       </c>
       <c r="K56">
         <v>6.88</v>
@@ -4299,7 +4299,7 @@
         <v>504</v>
       </c>
       <c r="J57">
-        <v>344.4</v>
+        <v>34440</v>
       </c>
       <c r="K57">
         <v>7</v>
@@ -4338,7 +4338,7 @@
         <v>513</v>
       </c>
       <c r="J58">
-        <v>350.55</v>
+        <v>35055</v>
       </c>
       <c r="K58">
         <v>7.13</v>
@@ -4377,7 +4377,7 @@
         <v>522</v>
       </c>
       <c r="J59">
-        <v>356.7</v>
+        <v>35670</v>
       </c>
       <c r="K59">
         <v>7.25</v>
@@ -4416,7 +4416,7 @@
         <v>531</v>
       </c>
       <c r="J60">
-        <v>362.85</v>
+        <v>36285</v>
       </c>
       <c r="K60">
         <v>7.38</v>
@@ -4455,7 +4455,7 @@
         <v>540</v>
       </c>
       <c r="J61">
-        <v>369</v>
+        <v>36900</v>
       </c>
       <c r="K61">
         <v>7.5</v>
@@ -4494,7 +4494,7 @@
         <v>549</v>
       </c>
       <c r="J62">
-        <v>375.15</v>
+        <v>37515</v>
       </c>
       <c r="K62">
         <v>7.63</v>
@@ -4533,7 +4533,7 @@
         <v>558</v>
       </c>
       <c r="J63">
-        <v>381.3</v>
+        <v>38130</v>
       </c>
       <c r="K63">
         <v>7.75</v>
@@ -4572,7 +4572,7 @@
         <v>567</v>
       </c>
       <c r="J64">
-        <v>387.45</v>
+        <v>38745</v>
       </c>
       <c r="K64">
         <v>7.88</v>
@@ -4611,7 +4611,7 @@
         <v>576</v>
       </c>
       <c r="J65">
-        <v>393.6</v>
+        <v>39360</v>
       </c>
       <c r="K65">
         <v>8</v>
@@ -4650,7 +4650,7 @@
         <v>585</v>
       </c>
       <c r="J66">
-        <v>399.75</v>
+        <v>39975</v>
       </c>
       <c r="K66">
         <v>8.13</v>
@@ -4689,7 +4689,7 @@
         <v>594</v>
       </c>
       <c r="J67">
-        <v>405.9</v>
+        <v>40590</v>
       </c>
       <c r="K67">
         <v>8.25</v>
@@ -4728,7 +4728,7 @@
         <v>603</v>
       </c>
       <c r="J68">
-        <v>412.05</v>
+        <v>41205</v>
       </c>
       <c r="K68">
         <v>8.38</v>
@@ -4767,7 +4767,7 @@
         <v>612</v>
       </c>
       <c r="J69">
-        <v>418.2</v>
+        <v>41820</v>
       </c>
       <c r="K69">
         <v>8.5</v>
@@ -4806,7 +4806,7 @@
         <v>621</v>
       </c>
       <c r="J70">
-        <v>424.35</v>
+        <v>42435</v>
       </c>
       <c r="K70">
         <v>8.63</v>
@@ -4845,7 +4845,7 @@
         <v>630</v>
       </c>
       <c r="J71">
-        <v>430.5</v>
+        <v>43050</v>
       </c>
       <c r="K71">
         <v>8.75</v>
@@ -4884,7 +4884,7 @@
         <v>639</v>
       </c>
       <c r="J72">
-        <v>436.65</v>
+        <v>43665</v>
       </c>
       <c r="K72">
         <v>8.88</v>
@@ -4923,7 +4923,7 @@
         <v>648</v>
       </c>
       <c r="J73">
-        <v>442.8</v>
+        <v>44280</v>
       </c>
       <c r="K73">
         <v>9</v>
@@ -4962,7 +4962,7 @@
         <v>657</v>
       </c>
       <c r="J74">
-        <v>448.95</v>
+        <v>44895</v>
       </c>
       <c r="K74">
         <v>9.13</v>
@@ -5001,7 +5001,7 @@
         <v>666</v>
       </c>
       <c r="J75">
-        <v>455.1</v>
+        <v>45510</v>
       </c>
       <c r="K75">
         <v>9.25</v>
@@ -5040,7 +5040,7 @@
         <v>675</v>
       </c>
       <c r="J76">
-        <v>461.25</v>
+        <v>46125</v>
       </c>
       <c r="K76">
         <v>9.38</v>
@@ -5079,7 +5079,7 @@
         <v>684</v>
       </c>
       <c r="J77">
-        <v>467.4</v>
+        <v>46740</v>
       </c>
       <c r="K77">
         <v>9.5</v>
@@ -5118,7 +5118,7 @@
         <v>693</v>
       </c>
       <c r="J78">
-        <v>473.55</v>
+        <v>47355</v>
       </c>
       <c r="K78">
         <v>9.63</v>
@@ -5157,7 +5157,7 @@
         <v>702</v>
       </c>
       <c r="J79">
-        <v>479.7</v>
+        <v>47970</v>
       </c>
       <c r="K79">
         <v>9.75</v>
@@ -5196,7 +5196,7 @@
         <v>711</v>
       </c>
       <c r="J80">
-        <v>485.85</v>
+        <v>48585</v>
       </c>
       <c r="K80">
         <v>9.88</v>
@@ -5235,7 +5235,7 @@
         <v>720</v>
       </c>
       <c r="J81">
-        <v>492</v>
+        <v>49200</v>
       </c>
       <c r="K81">
         <v>10</v>
@@ -5274,7 +5274,7 @@
         <v>729</v>
       </c>
       <c r="J82">
-        <v>498.15</v>
+        <v>49815</v>
       </c>
       <c r="K82">
         <v>10.13</v>
@@ -5313,7 +5313,7 @@
         <v>738</v>
       </c>
       <c r="J83">
-        <v>504.3</v>
+        <v>50430</v>
       </c>
       <c r="K83">
         <v>10.25</v>
@@ -5352,7 +5352,7 @@
         <v>747</v>
       </c>
       <c r="J84">
-        <v>510.45</v>
+        <v>51045</v>
       </c>
       <c r="K84">
         <v>10.38</v>
@@ -5391,7 +5391,7 @@
         <v>756</v>
       </c>
       <c r="J85">
-        <v>516.6</v>
+        <v>51660</v>
       </c>
       <c r="K85">
         <v>10.5</v>
@@ -5430,7 +5430,7 @@
         <v>765</v>
       </c>
       <c r="J86">
-        <v>522.75</v>
+        <v>52275</v>
       </c>
       <c r="K86">
         <v>10.63</v>
@@ -5469,7 +5469,7 @@
         <v>774</v>
       </c>
       <c r="J87">
-        <v>528.9</v>
+        <v>52890</v>
       </c>
       <c r="K87">
         <v>10.75</v>
@@ -5508,7 +5508,7 @@
         <v>783</v>
       </c>
       <c r="J88">
-        <v>535.05</v>
+        <v>53505</v>
       </c>
       <c r="K88">
         <v>10.88</v>
@@ -5547,7 +5547,7 @@
         <v>792</v>
       </c>
       <c r="J89">
-        <v>541.2</v>
+        <v>54120</v>
       </c>
       <c r="K89">
         <v>11</v>
@@ -5586,7 +5586,7 @@
         <v>801</v>
       </c>
       <c r="J90">
-        <v>547.35</v>
+        <v>54735</v>
       </c>
       <c r="K90">
         <v>11.13</v>
@@ -5625,7 +5625,7 @@
         <v>810</v>
       </c>
       <c r="J91">
-        <v>553.5</v>
+        <v>55350</v>
       </c>
       <c r="K91">
         <v>11.25</v>
@@ -5664,7 +5664,7 @@
         <v>819</v>
       </c>
       <c r="J92">
-        <v>559.65</v>
+        <v>55965</v>
       </c>
       <c r="K92">
         <v>11.38</v>
@@ -5703,7 +5703,7 @@
         <v>828</v>
       </c>
       <c r="J93">
-        <v>565.8</v>
+        <v>56580</v>
       </c>
       <c r="K93">
         <v>11.5</v>
@@ -5742,7 +5742,7 @@
         <v>837</v>
       </c>
       <c r="J94">
-        <v>571.95</v>
+        <v>57195</v>
       </c>
       <c r="K94">
         <v>11.63</v>
@@ -5781,7 +5781,7 @@
         <v>846</v>
       </c>
       <c r="J95">
-        <v>578.1</v>
+        <v>57810</v>
       </c>
       <c r="K95">
         <v>11.75</v>
@@ -5820,7 +5820,7 @@
         <v>855</v>
       </c>
       <c r="J96">
-        <v>584.25</v>
+        <v>58425</v>
       </c>
       <c r="K96">
         <v>11.88</v>
@@ -5859,7 +5859,7 @@
         <v>864</v>
       </c>
       <c r="J97">
-        <v>590.4</v>
+        <v>59040</v>
       </c>
       <c r="K97">
         <v>12</v>
@@ -5898,7 +5898,7 @@
         <v>873</v>
       </c>
       <c r="J98">
-        <v>596.55</v>
+        <v>59655</v>
       </c>
       <c r="K98">
         <v>12.13</v>
@@ -5937,7 +5937,7 @@
         <v>882</v>
       </c>
       <c r="J99">
-        <v>602.7</v>
+        <v>60270</v>
       </c>
       <c r="K99">
         <v>12.25</v>
@@ -5976,7 +5976,7 @@
         <v>891</v>
       </c>
       <c r="J100">
-        <v>608.85</v>
+        <v>60885</v>
       </c>
       <c r="K100">
         <v>12.38</v>
@@ -6015,7 +6015,7 @@
         <v>900</v>
       </c>
       <c r="J101">
-        <v>615</v>
+        <v>61500</v>
       </c>
       <c r="K101">
         <v>12.5</v>
@@ -6054,7 +6054,7 @@
         <v>909</v>
       </c>
       <c r="J102">
-        <v>621.15</v>
+        <v>62115</v>
       </c>
       <c r="K102">
         <v>12.63</v>
@@ -6093,7 +6093,7 @@
         <v>918</v>
       </c>
       <c r="J103">
-        <v>627.3</v>
+        <v>62730</v>
       </c>
       <c r="K103">
         <v>12.75</v>
@@ -6132,7 +6132,7 @@
         <v>927</v>
       </c>
       <c r="J104">
-        <v>633.45</v>
+        <v>63345</v>
       </c>
       <c r="K104">
         <v>12.88</v>
@@ -6171,7 +6171,7 @@
         <v>936</v>
       </c>
       <c r="J105">
-        <v>639.6</v>
+        <v>63960</v>
       </c>
       <c r="K105">
         <v>13</v>
@@ -6210,7 +6210,7 @@
         <v>945</v>
       </c>
       <c r="J106">
-        <v>645.75</v>
+        <v>64575</v>
       </c>
       <c r="K106">
         <v>13.13</v>
@@ -6249,7 +6249,7 @@
         <v>954</v>
       </c>
       <c r="J107">
-        <v>651.9</v>
+        <v>65190</v>
       </c>
       <c r="K107">
         <v>13.25</v>
@@ -6288,7 +6288,7 @@
         <v>963</v>
       </c>
       <c r="J108">
-        <v>658.05</v>
+        <v>65805</v>
       </c>
       <c r="K108">
         <v>13.38</v>
@@ -6327,7 +6327,7 @@
         <v>972</v>
       </c>
       <c r="J109">
-        <v>664.2</v>
+        <v>66420</v>
       </c>
       <c r="K109">
         <v>13.5</v>
@@ -6366,7 +6366,7 @@
         <v>981</v>
       </c>
       <c r="J110">
-        <v>670.35</v>
+        <v>67035</v>
       </c>
       <c r="K110">
         <v>13.63</v>
@@ -6405,7 +6405,7 @@
         <v>990</v>
       </c>
       <c r="J111">
-        <v>676.5</v>
+        <v>67650</v>
       </c>
       <c r="K111">
         <v>13.75</v>
@@ -6444,7 +6444,7 @@
         <v>999</v>
       </c>
       <c r="J112">
-        <v>682.65</v>
+        <v>68265</v>
       </c>
       <c r="K112">
         <v>13.88</v>
@@ -6483,7 +6483,7 @@
         <v>1008</v>
       </c>
       <c r="J113">
-        <v>688.8</v>
+        <v>68880</v>
       </c>
       <c r="K113">
         <v>14</v>
@@ -6522,7 +6522,7 @@
         <v>1017</v>
       </c>
       <c r="J114">
-        <v>694.95</v>
+        <v>69495</v>
       </c>
       <c r="K114">
         <v>14.13</v>
@@ -6561,7 +6561,7 @@
         <v>1026</v>
       </c>
       <c r="J115">
-        <v>701.1</v>
+        <v>70110</v>
       </c>
       <c r="K115">
         <v>14.25</v>
@@ -6600,7 +6600,7 @@
         <v>1035</v>
       </c>
       <c r="J116">
-        <v>707.25</v>
+        <v>70725</v>
       </c>
       <c r="K116">
         <v>14.38</v>
@@ -6639,7 +6639,7 @@
         <v>1044</v>
       </c>
       <c r="J117">
-        <v>713.4</v>
+        <v>71340</v>
       </c>
       <c r="K117">
         <v>14.5</v>
@@ -6678,7 +6678,7 @@
         <v>1053</v>
       </c>
       <c r="J118">
-        <v>719.55</v>
+        <v>71955</v>
       </c>
       <c r="K118">
         <v>14.63</v>
@@ -6717,7 +6717,7 @@
         <v>1062</v>
       </c>
       <c r="J119">
-        <v>725.7</v>
+        <v>72570</v>
       </c>
       <c r="K119">
         <v>14.75</v>
@@ -6756,7 +6756,7 @@
         <v>1071</v>
       </c>
       <c r="J120">
-        <v>731.85</v>
+        <v>73185</v>
       </c>
       <c r="K120">
         <v>14.88</v>
@@ -6795,7 +6795,7 @@
         <v>1080</v>
       </c>
       <c r="J121">
-        <v>738</v>
+        <v>73800</v>
       </c>
       <c r="K121">
         <v>15</v>
@@ -6834,7 +6834,7 @@
         <v>13</v>
       </c>
       <c r="J122">
-        <v>11</v>
+        <v>1100</v>
       </c>
       <c r="K122">
         <v>0.25</v>
@@ -6873,7 +6873,7 @@
         <v>26</v>
       </c>
       <c r="J123">
-        <v>22</v>
+        <v>2200</v>
       </c>
       <c r="K123">
         <v>0.5</v>
@@ -6912,7 +6912,7 @@
         <v>39</v>
       </c>
       <c r="J124">
-        <v>33</v>
+        <v>3300</v>
       </c>
       <c r="K124">
         <v>0.75</v>
@@ -6951,7 +6951,7 @@
         <v>52</v>
       </c>
       <c r="J125">
-        <v>44</v>
+        <v>4400</v>
       </c>
       <c r="K125">
         <v>1</v>
@@ -6990,7 +6990,7 @@
         <v>65</v>
       </c>
       <c r="J126">
-        <v>55</v>
+        <v>5500</v>
       </c>
       <c r="K126">
         <v>1.25</v>
@@ -7029,7 +7029,7 @@
         <v>78</v>
       </c>
       <c r="J127">
-        <v>66</v>
+        <v>6600</v>
       </c>
       <c r="K127">
         <v>1.5</v>
@@ -7068,7 +7068,7 @@
         <v>91</v>
       </c>
       <c r="J128">
-        <v>77</v>
+        <v>7700</v>
       </c>
       <c r="K128">
         <v>1.75</v>
@@ -7107,7 +7107,7 @@
         <v>104</v>
       </c>
       <c r="J129">
-        <v>88</v>
+        <v>8800</v>
       </c>
       <c r="K129">
         <v>2</v>
@@ -7146,7 +7146,7 @@
         <v>117</v>
       </c>
       <c r="J130">
-        <v>99</v>
+        <v>9900</v>
       </c>
       <c r="K130">
         <v>2.25</v>
@@ -7185,7 +7185,7 @@
         <v>130</v>
       </c>
       <c r="J131">
-        <v>110</v>
+        <v>11000</v>
       </c>
       <c r="K131">
         <v>2.5</v>
@@ -7224,7 +7224,7 @@
         <v>143</v>
       </c>
       <c r="J132">
-        <v>121</v>
+        <v>12100</v>
       </c>
       <c r="K132">
         <v>2.75</v>
@@ -7263,7 +7263,7 @@
         <v>156</v>
       </c>
       <c r="J133">
-        <v>132</v>
+        <v>13200</v>
       </c>
       <c r="K133">
         <v>3</v>
@@ -7302,7 +7302,7 @@
         <v>169</v>
       </c>
       <c r="J134">
-        <v>143</v>
+        <v>14300</v>
       </c>
       <c r="K134">
         <v>3.25</v>
@@ -7341,7 +7341,7 @@
         <v>182</v>
       </c>
       <c r="J135">
-        <v>154</v>
+        <v>15400</v>
       </c>
       <c r="K135">
         <v>3.5</v>
@@ -7380,7 +7380,7 @@
         <v>195</v>
       </c>
       <c r="J136">
-        <v>165</v>
+        <v>16500</v>
       </c>
       <c r="K136">
         <v>3.75</v>
@@ -7419,7 +7419,7 @@
         <v>208</v>
       </c>
       <c r="J137">
-        <v>176</v>
+        <v>17600</v>
       </c>
       <c r="K137">
         <v>4</v>
@@ -7458,7 +7458,7 @@
         <v>221</v>
       </c>
       <c r="J138">
-        <v>187</v>
+        <v>18700</v>
       </c>
       <c r="K138">
         <v>4.25</v>
@@ -7497,7 +7497,7 @@
         <v>234</v>
       </c>
       <c r="J139">
-        <v>198</v>
+        <v>19800</v>
       </c>
       <c r="K139">
         <v>4.5</v>
@@ -7536,7 +7536,7 @@
         <v>247</v>
       </c>
       <c r="J140">
-        <v>209</v>
+        <v>20900</v>
       </c>
       <c r="K140">
         <v>4.75</v>
@@ -7575,7 +7575,7 @@
         <v>260</v>
       </c>
       <c r="J141">
-        <v>220</v>
+        <v>22000</v>
       </c>
       <c r="K141">
         <v>5</v>
@@ -7614,7 +7614,7 @@
         <v>273</v>
       </c>
       <c r="J142">
-        <v>231</v>
+        <v>23100</v>
       </c>
       <c r="K142">
         <v>5.25</v>
@@ -7653,7 +7653,7 @@
         <v>286</v>
       </c>
       <c r="J143">
-        <v>242</v>
+        <v>24200</v>
       </c>
       <c r="K143">
         <v>5.5</v>
@@ -7692,7 +7692,7 @@
         <v>299</v>
       </c>
       <c r="J144">
-        <v>253</v>
+        <v>25300</v>
       </c>
       <c r="K144">
         <v>5.75</v>
@@ -7731,7 +7731,7 @@
         <v>312</v>
       </c>
       <c r="J145">
-        <v>264</v>
+        <v>26400</v>
       </c>
       <c r="K145">
         <v>6</v>
@@ -7770,7 +7770,7 @@
         <v>325</v>
       </c>
       <c r="J146">
-        <v>275</v>
+        <v>27500</v>
       </c>
       <c r="K146">
         <v>6.25</v>
@@ -7809,7 +7809,7 @@
         <v>338</v>
       </c>
       <c r="J147">
-        <v>286</v>
+        <v>28600</v>
       </c>
       <c r="K147">
         <v>6.5</v>
@@ -7848,7 +7848,7 @@
         <v>351</v>
       </c>
       <c r="J148">
-        <v>297</v>
+        <v>29700</v>
       </c>
       <c r="K148">
         <v>6.75</v>
@@ -7887,7 +7887,7 @@
         <v>364</v>
       </c>
       <c r="J149">
-        <v>308</v>
+        <v>30800</v>
       </c>
       <c r="K149">
         <v>7</v>
@@ -7926,7 +7926,7 @@
         <v>377</v>
       </c>
       <c r="J150">
-        <v>319</v>
+        <v>31900</v>
       </c>
       <c r="K150">
         <v>7.25</v>
@@ -7965,7 +7965,7 @@
         <v>390</v>
       </c>
       <c r="J151">
-        <v>330</v>
+        <v>33000</v>
       </c>
       <c r="K151">
         <v>7.5</v>
@@ -8004,7 +8004,7 @@
         <v>403</v>
       </c>
       <c r="J152">
-        <v>341</v>
+        <v>34100</v>
       </c>
       <c r="K152">
         <v>7.75</v>
@@ -8043,7 +8043,7 @@
         <v>416</v>
       </c>
       <c r="J153">
-        <v>352</v>
+        <v>35200</v>
       </c>
       <c r="K153">
         <v>8</v>
@@ -8082,7 +8082,7 @@
         <v>429</v>
       </c>
       <c r="J154">
-        <v>363</v>
+        <v>36300</v>
       </c>
       <c r="K154">
         <v>8.25</v>
@@ -8121,7 +8121,7 @@
         <v>442</v>
       </c>
       <c r="J155">
-        <v>374</v>
+        <v>37400</v>
       </c>
       <c r="K155">
         <v>8.5</v>
@@ -8160,7 +8160,7 @@
         <v>455</v>
       </c>
       <c r="J156">
-        <v>385</v>
+        <v>38500</v>
       </c>
       <c r="K156">
         <v>8.75</v>
@@ -8199,7 +8199,7 @@
         <v>468</v>
       </c>
       <c r="J157">
-        <v>396</v>
+        <v>39600</v>
       </c>
       <c r="K157">
         <v>9</v>
@@ -8238,7 +8238,7 @@
         <v>481</v>
       </c>
       <c r="J158">
-        <v>407</v>
+        <v>40700</v>
       </c>
       <c r="K158">
         <v>9.25</v>
@@ -8277,7 +8277,7 @@
         <v>494</v>
       </c>
       <c r="J159">
-        <v>418</v>
+        <v>41800</v>
       </c>
       <c r="K159">
         <v>9.5</v>
@@ -8316,7 +8316,7 @@
         <v>507</v>
       </c>
       <c r="J160">
-        <v>429</v>
+        <v>42900</v>
       </c>
       <c r="K160">
         <v>9.75</v>
@@ -8355,7 +8355,7 @@
         <v>520</v>
       </c>
       <c r="J161">
-        <v>440</v>
+        <v>44000</v>
       </c>
       <c r="K161">
         <v>10</v>
@@ -8394,7 +8394,7 @@
         <v>533</v>
       </c>
       <c r="J162">
-        <v>451</v>
+        <v>45100</v>
       </c>
       <c r="K162">
         <v>10.25</v>
@@ -8433,7 +8433,7 @@
         <v>546</v>
       </c>
       <c r="J163">
-        <v>462</v>
+        <v>46200</v>
       </c>
       <c r="K163">
         <v>10.5</v>
@@ -8472,7 +8472,7 @@
         <v>559</v>
       </c>
       <c r="J164">
-        <v>473</v>
+        <v>47300</v>
       </c>
       <c r="K164">
         <v>10.75</v>
@@ -8511,7 +8511,7 @@
         <v>572</v>
       </c>
       <c r="J165">
-        <v>484</v>
+        <v>48400</v>
       </c>
       <c r="K165">
         <v>11</v>
@@ -8550,7 +8550,7 @@
         <v>585</v>
       </c>
       <c r="J166">
-        <v>495</v>
+        <v>49500</v>
       </c>
       <c r="K166">
         <v>11.25</v>
@@ -8589,7 +8589,7 @@
         <v>598</v>
       </c>
       <c r="J167">
-        <v>506</v>
+        <v>50600</v>
       </c>
       <c r="K167">
         <v>11.5</v>
@@ -8628,7 +8628,7 @@
         <v>611</v>
       </c>
       <c r="J168">
-        <v>517</v>
+        <v>51700</v>
       </c>
       <c r="K168">
         <v>11.75</v>
@@ -8667,7 +8667,7 @@
         <v>624</v>
       </c>
       <c r="J169">
-        <v>528</v>
+        <v>52800</v>
       </c>
       <c r="K169">
         <v>12</v>
@@ -8706,7 +8706,7 @@
         <v>637</v>
       </c>
       <c r="J170">
-        <v>539</v>
+        <v>53900</v>
       </c>
       <c r="K170">
         <v>12.25</v>
@@ -8745,7 +8745,7 @@
         <v>650</v>
       </c>
       <c r="J171">
-        <v>550</v>
+        <v>55000</v>
       </c>
       <c r="K171">
         <v>12.5</v>
@@ -8784,7 +8784,7 @@
         <v>663</v>
       </c>
       <c r="J172">
-        <v>561</v>
+        <v>56100</v>
       </c>
       <c r="K172">
         <v>12.75</v>
@@ -8823,7 +8823,7 @@
         <v>676</v>
       </c>
       <c r="J173">
-        <v>572</v>
+        <v>57200</v>
       </c>
       <c r="K173">
         <v>13</v>
@@ -8862,7 +8862,7 @@
         <v>689</v>
       </c>
       <c r="J174">
-        <v>583</v>
+        <v>58300</v>
       </c>
       <c r="K174">
         <v>13.25</v>
@@ -8901,7 +8901,7 @@
         <v>702</v>
       </c>
       <c r="J175">
-        <v>594</v>
+        <v>59400</v>
       </c>
       <c r="K175">
         <v>13.5</v>
@@ -8940,7 +8940,7 @@
         <v>715</v>
       </c>
       <c r="J176">
-        <v>605</v>
+        <v>60500</v>
       </c>
       <c r="K176">
         <v>13.75</v>
@@ -8979,7 +8979,7 @@
         <v>728</v>
       </c>
       <c r="J177">
-        <v>616</v>
+        <v>61600</v>
       </c>
       <c r="K177">
         <v>14</v>
@@ -9018,7 +9018,7 @@
         <v>741</v>
       </c>
       <c r="J178">
-        <v>627</v>
+        <v>62700</v>
       </c>
       <c r="K178">
         <v>14.25</v>
@@ -9057,7 +9057,7 @@
         <v>754</v>
       </c>
       <c r="J179">
-        <v>638</v>
+        <v>63800</v>
       </c>
       <c r="K179">
         <v>14.5</v>
@@ -9096,7 +9096,7 @@
         <v>767</v>
       </c>
       <c r="J180">
-        <v>649</v>
+        <v>64900</v>
       </c>
       <c r="K180">
         <v>14.75</v>
@@ -9135,7 +9135,7 @@
         <v>780</v>
       </c>
       <c r="J181">
-        <v>660</v>
+        <v>66000</v>
       </c>
       <c r="K181">
         <v>15</v>
@@ -9174,7 +9174,7 @@
         <v>793</v>
       </c>
       <c r="J182">
-        <v>671</v>
+        <v>67100</v>
       </c>
       <c r="K182">
         <v>15.25</v>
@@ -9213,7 +9213,7 @@
         <v>806</v>
       </c>
       <c r="J183">
-        <v>682</v>
+        <v>68200</v>
       </c>
       <c r="K183">
         <v>15.5</v>
@@ -9252,7 +9252,7 @@
         <v>819</v>
       </c>
       <c r="J184">
-        <v>693</v>
+        <v>69300</v>
       </c>
       <c r="K184">
         <v>15.75</v>
@@ -9291,7 +9291,7 @@
         <v>832</v>
       </c>
       <c r="J185">
-        <v>704</v>
+        <v>70400</v>
       </c>
       <c r="K185">
         <v>16</v>
@@ -9330,7 +9330,7 @@
         <v>845</v>
       </c>
       <c r="J186">
-        <v>715</v>
+        <v>71500</v>
       </c>
       <c r="K186">
         <v>16.25</v>
@@ -9369,7 +9369,7 @@
         <v>858</v>
       </c>
       <c r="J187">
-        <v>726</v>
+        <v>72600</v>
       </c>
       <c r="K187">
         <v>16.5</v>
@@ -9408,7 +9408,7 @@
         <v>871</v>
       </c>
       <c r="J188">
-        <v>737</v>
+        <v>73700</v>
       </c>
       <c r="K188">
         <v>16.75</v>
@@ -9447,7 +9447,7 @@
         <v>884</v>
       </c>
       <c r="J189">
-        <v>748</v>
+        <v>74800</v>
       </c>
       <c r="K189">
         <v>17</v>
@@ -9486,7 +9486,7 @@
         <v>897</v>
       </c>
       <c r="J190">
-        <v>759</v>
+        <v>75900</v>
       </c>
       <c r="K190">
         <v>17.25</v>
@@ -9525,7 +9525,7 @@
         <v>910</v>
       </c>
       <c r="J191">
-        <v>770</v>
+        <v>77000</v>
       </c>
       <c r="K191">
         <v>17.5</v>
@@ -9564,7 +9564,7 @@
         <v>923</v>
       </c>
       <c r="J192">
-        <v>781</v>
+        <v>78100</v>
       </c>
       <c r="K192">
         <v>17.75</v>
@@ -9603,7 +9603,7 @@
         <v>936</v>
       </c>
       <c r="J193">
-        <v>792</v>
+        <v>79200</v>
       </c>
       <c r="K193">
         <v>18</v>
@@ -9642,7 +9642,7 @@
         <v>949</v>
       </c>
       <c r="J194">
-        <v>803</v>
+        <v>80300</v>
       </c>
       <c r="K194">
         <v>18.25</v>
@@ -9681,7 +9681,7 @@
         <v>962</v>
       </c>
       <c r="J195">
-        <v>814</v>
+        <v>81400</v>
       </c>
       <c r="K195">
         <v>18.5</v>
@@ -9720,7 +9720,7 @@
         <v>975</v>
       </c>
       <c r="J196">
-        <v>825</v>
+        <v>82500</v>
       </c>
       <c r="K196">
         <v>18.75</v>
@@ -9759,7 +9759,7 @@
         <v>988</v>
       </c>
       <c r="J197">
-        <v>836</v>
+        <v>83600</v>
       </c>
       <c r="K197">
         <v>19</v>
@@ -9798,7 +9798,7 @@
         <v>1001</v>
       </c>
       <c r="J198">
-        <v>847</v>
+        <v>84700</v>
       </c>
       <c r="K198">
         <v>19.25</v>
@@ -9837,7 +9837,7 @@
         <v>1014</v>
       </c>
       <c r="J199">
-        <v>858</v>
+        <v>85800</v>
       </c>
       <c r="K199">
         <v>19.5</v>
@@ -9876,7 +9876,7 @@
         <v>1027</v>
       </c>
       <c r="J200">
-        <v>869</v>
+        <v>86900</v>
       </c>
       <c r="K200">
         <v>19.75</v>
@@ -9915,7 +9915,7 @@
         <v>1040</v>
       </c>
       <c r="J201">
-        <v>880</v>
+        <v>88000</v>
       </c>
       <c r="K201">
         <v>20</v>
@@ -9954,7 +9954,7 @@
         <v>1053</v>
       </c>
       <c r="J202">
-        <v>891</v>
+        <v>89100</v>
       </c>
       <c r="K202">
         <v>20.25</v>
@@ -9993,7 +9993,7 @@
         <v>1066</v>
       </c>
       <c r="J203">
-        <v>902</v>
+        <v>90200</v>
       </c>
       <c r="K203">
         <v>20.5</v>
@@ -10032,7 +10032,7 @@
         <v>1079</v>
       </c>
       <c r="J204">
-        <v>913</v>
+        <v>91300</v>
       </c>
       <c r="K204">
         <v>20.75</v>
@@ -10071,7 +10071,7 @@
         <v>1092</v>
       </c>
       <c r="J205">
-        <v>924</v>
+        <v>92400</v>
       </c>
       <c r="K205">
         <v>21</v>
@@ -10110,7 +10110,7 @@
         <v>1105</v>
       </c>
       <c r="J206">
-        <v>935</v>
+        <v>93500</v>
       </c>
       <c r="K206">
         <v>21.25</v>
@@ -10149,7 +10149,7 @@
         <v>1118</v>
       </c>
       <c r="J207">
-        <v>946</v>
+        <v>94600</v>
       </c>
       <c r="K207">
         <v>21.5</v>
@@ -10188,7 +10188,7 @@
         <v>1131</v>
       </c>
       <c r="J208">
-        <v>957</v>
+        <v>95700</v>
       </c>
       <c r="K208">
         <v>21.75</v>
@@ -10227,7 +10227,7 @@
         <v>1144</v>
       </c>
       <c r="J209">
-        <v>968</v>
+        <v>96800</v>
       </c>
       <c r="K209">
         <v>22</v>
@@ -10266,7 +10266,7 @@
         <v>1157</v>
       </c>
       <c r="J210">
-        <v>979</v>
+        <v>97900</v>
       </c>
       <c r="K210">
         <v>22.25</v>
@@ -10305,7 +10305,7 @@
         <v>1170</v>
       </c>
       <c r="J211">
-        <v>990</v>
+        <v>99000</v>
       </c>
       <c r="K211">
         <v>22.5</v>
@@ -10344,7 +10344,7 @@
         <v>1183</v>
       </c>
       <c r="J212">
-        <v>1001</v>
+        <v>100100</v>
       </c>
       <c r="K212">
         <v>22.75</v>
@@ -10383,7 +10383,7 @@
         <v>1196</v>
       </c>
       <c r="J213">
-        <v>1012</v>
+        <v>101200</v>
       </c>
       <c r="K213">
         <v>23</v>
@@ -10422,7 +10422,7 @@
         <v>1209</v>
       </c>
       <c r="J214">
-        <v>1023</v>
+        <v>102300</v>
       </c>
       <c r="K214">
         <v>23.25</v>
@@ -10461,7 +10461,7 @@
         <v>1222</v>
       </c>
       <c r="J215">
-        <v>1034</v>
+        <v>103400</v>
       </c>
       <c r="K215">
         <v>23.5</v>
@@ -10500,7 +10500,7 @@
         <v>1235</v>
       </c>
       <c r="J216">
-        <v>1045</v>
+        <v>104500</v>
       </c>
       <c r="K216">
         <v>23.75</v>
@@ -10539,7 +10539,7 @@
         <v>1248</v>
       </c>
       <c r="J217">
-        <v>1056</v>
+        <v>105600</v>
       </c>
       <c r="K217">
         <v>24</v>
@@ -10578,7 +10578,7 @@
         <v>1261</v>
       </c>
       <c r="J218">
-        <v>1067</v>
+        <v>106700</v>
       </c>
       <c r="K218">
         <v>24.25</v>
@@ -10617,7 +10617,7 @@
         <v>1274</v>
       </c>
       <c r="J219">
-        <v>1078</v>
+        <v>107800</v>
       </c>
       <c r="K219">
         <v>24.5</v>
@@ -10656,7 +10656,7 @@
         <v>1287</v>
       </c>
       <c r="J220">
-        <v>1089</v>
+        <v>108900</v>
       </c>
       <c r="K220">
         <v>24.75</v>
@@ -10695,7 +10695,7 @@
         <v>1300</v>
       </c>
       <c r="J221">
-        <v>1100</v>
+        <v>110000</v>
       </c>
       <c r="K221">
         <v>25</v>
@@ -10734,7 +10734,7 @@
         <v>1313</v>
       </c>
       <c r="J222">
-        <v>1111</v>
+        <v>111100</v>
       </c>
       <c r="K222">
         <v>25.25</v>
@@ -10773,7 +10773,7 @@
         <v>1326</v>
       </c>
       <c r="J223">
-        <v>1122</v>
+        <v>112200</v>
       </c>
       <c r="K223">
         <v>25.5</v>
@@ -10812,7 +10812,7 @@
         <v>1339</v>
       </c>
       <c r="J224">
-        <v>1133</v>
+        <v>113300</v>
       </c>
       <c r="K224">
         <v>25.75</v>
@@ -10851,7 +10851,7 @@
         <v>1352</v>
       </c>
       <c r="J225">
-        <v>1144</v>
+        <v>114400</v>
       </c>
       <c r="K225">
         <v>26</v>
@@ -10890,7 +10890,7 @@
         <v>1365</v>
       </c>
       <c r="J226">
-        <v>1155</v>
+        <v>115500</v>
       </c>
       <c r="K226">
         <v>26.25</v>
@@ -10929,7 +10929,7 @@
         <v>1378</v>
       </c>
       <c r="J227">
-        <v>1166</v>
+        <v>116600</v>
       </c>
       <c r="K227">
         <v>26.5</v>
@@ -10968,7 +10968,7 @@
         <v>1391</v>
       </c>
       <c r="J228">
-        <v>1177</v>
+        <v>117700</v>
       </c>
       <c r="K228">
         <v>26.75</v>
@@ -11007,7 +11007,7 @@
         <v>1404</v>
       </c>
       <c r="J229">
-        <v>1188</v>
+        <v>118800</v>
       </c>
       <c r="K229">
         <v>27</v>
@@ -11046,7 +11046,7 @@
         <v>1417</v>
       </c>
       <c r="J230">
-        <v>1199</v>
+        <v>119900</v>
       </c>
       <c r="K230">
         <v>27.25</v>
@@ -11085,7 +11085,7 @@
         <v>1430</v>
       </c>
       <c r="J231">
-        <v>1210</v>
+        <v>121000</v>
       </c>
       <c r="K231">
         <v>27.5</v>
@@ -11124,7 +11124,7 @@
         <v>1443</v>
       </c>
       <c r="J232">
-        <v>1221</v>
+        <v>122100</v>
       </c>
       <c r="K232">
         <v>27.75</v>
@@ -11163,7 +11163,7 @@
         <v>1456</v>
       </c>
       <c r="J233">
-        <v>1232</v>
+        <v>123200</v>
       </c>
       <c r="K233">
         <v>28</v>
@@ -11202,7 +11202,7 @@
         <v>1469</v>
       </c>
       <c r="J234">
-        <v>1243</v>
+        <v>124300</v>
       </c>
       <c r="K234">
         <v>28.25</v>
@@ -11241,7 +11241,7 @@
         <v>1482</v>
       </c>
       <c r="J235">
-        <v>1254</v>
+        <v>125400</v>
       </c>
       <c r="K235">
         <v>28.5</v>
@@ -11280,7 +11280,7 @@
         <v>1495</v>
       </c>
       <c r="J236">
-        <v>1265</v>
+        <v>126500</v>
       </c>
       <c r="K236">
         <v>28.75</v>
@@ -11319,7 +11319,7 @@
         <v>1508</v>
       </c>
       <c r="J237">
-        <v>1276</v>
+        <v>127600</v>
       </c>
       <c r="K237">
         <v>29</v>
@@ -11358,7 +11358,7 @@
         <v>1521</v>
       </c>
       <c r="J238">
-        <v>1287</v>
+        <v>128700</v>
       </c>
       <c r="K238">
         <v>29.25</v>
@@ -11397,7 +11397,7 @@
         <v>1534</v>
       </c>
       <c r="J239">
-        <v>1298</v>
+        <v>129800</v>
       </c>
       <c r="K239">
         <v>29.5</v>
@@ -11436,7 +11436,7 @@
         <v>1547</v>
       </c>
       <c r="J240">
-        <v>1309</v>
+        <v>130900</v>
       </c>
       <c r="K240">
         <v>29.75</v>
@@ -11475,7 +11475,7 @@
         <v>1560</v>
       </c>
       <c r="J241">
-        <v>1320</v>
+        <v>132000</v>
       </c>
       <c r="K241">
         <v>30</v>
@@ -11514,7 +11514,7 @@
         <v>17</v>
       </c>
       <c r="J242">
-        <v>13</v>
+        <v>1300</v>
       </c>
       <c r="K242">
         <v>0.75</v>
@@ -11553,7 +11553,7 @@
         <v>34</v>
       </c>
       <c r="J243">
-        <v>26</v>
+        <v>2600</v>
       </c>
       <c r="K243">
         <v>1.5</v>
@@ -11592,7 +11592,7 @@
         <v>51</v>
       </c>
       <c r="J244">
-        <v>39</v>
+        <v>3900</v>
       </c>
       <c r="K244">
         <v>2.25</v>
@@ -11631,7 +11631,7 @@
         <v>68</v>
       </c>
       <c r="J245">
-        <v>52</v>
+        <v>5200</v>
       </c>
       <c r="K245">
         <v>3</v>
@@ -11670,7 +11670,7 @@
         <v>85</v>
       </c>
       <c r="J246">
-        <v>65</v>
+        <v>6500</v>
       </c>
       <c r="K246">
         <v>3.75</v>
@@ -11709,7 +11709,7 @@
         <v>102</v>
       </c>
       <c r="J247">
-        <v>78</v>
+        <v>7800</v>
       </c>
       <c r="K247">
         <v>4.5</v>
@@ -11748,7 +11748,7 @@
         <v>119</v>
       </c>
       <c r="J248">
-        <v>91</v>
+        <v>9100</v>
       </c>
       <c r="K248">
         <v>5.25</v>
@@ -11787,7 +11787,7 @@
         <v>136</v>
       </c>
       <c r="J249">
-        <v>104</v>
+        <v>10400</v>
       </c>
       <c r="K249">
         <v>6</v>
@@ -11826,7 +11826,7 @@
         <v>153</v>
       </c>
       <c r="J250">
-        <v>117</v>
+        <v>11700</v>
       </c>
       <c r="K250">
         <v>6.75</v>
@@ -11865,7 +11865,7 @@
         <v>170</v>
       </c>
       <c r="J251">
-        <v>130</v>
+        <v>13000</v>
       </c>
       <c r="K251">
         <v>7.5</v>
@@ -11904,7 +11904,7 @@
         <v>187</v>
       </c>
       <c r="J252">
-        <v>143</v>
+        <v>14300</v>
       </c>
       <c r="K252">
         <v>8.25</v>
@@ -11943,7 +11943,7 @@
         <v>204</v>
       </c>
       <c r="J253">
-        <v>156</v>
+        <v>15600</v>
       </c>
       <c r="K253">
         <v>9</v>
@@ -11982,7 +11982,7 @@
         <v>221</v>
       </c>
       <c r="J254">
-        <v>169</v>
+        <v>16900</v>
       </c>
       <c r="K254">
         <v>9.75</v>
@@ -12021,7 +12021,7 @@
         <v>238</v>
       </c>
       <c r="J255">
-        <v>182</v>
+        <v>18200</v>
       </c>
       <c r="K255">
         <v>10.5</v>
@@ -12060,7 +12060,7 @@
         <v>255</v>
       </c>
       <c r="J256">
-        <v>195</v>
+        <v>19500</v>
       </c>
       <c r="K256">
         <v>11.25</v>
@@ -12099,7 +12099,7 @@
         <v>272</v>
       </c>
       <c r="J257">
-        <v>208</v>
+        <v>20800</v>
       </c>
       <c r="K257">
         <v>12</v>
@@ -12138,7 +12138,7 @@
         <v>289</v>
       </c>
       <c r="J258">
-        <v>221</v>
+        <v>22100</v>
       </c>
       <c r="K258">
         <v>12.75</v>
@@ -12177,7 +12177,7 @@
         <v>306</v>
       </c>
       <c r="J259">
-        <v>234</v>
+        <v>23400</v>
       </c>
       <c r="K259">
         <v>13.5</v>
@@ -12216,7 +12216,7 @@
         <v>323</v>
       </c>
       <c r="J260">
-        <v>247</v>
+        <v>24700</v>
       </c>
       <c r="K260">
         <v>14.25</v>
@@ -12255,7 +12255,7 @@
         <v>340</v>
       </c>
       <c r="J261">
-        <v>260</v>
+        <v>26000</v>
       </c>
       <c r="K261">
         <v>15</v>
@@ -12294,7 +12294,7 @@
         <v>357</v>
       </c>
       <c r="J262">
-        <v>273</v>
+        <v>27300</v>
       </c>
       <c r="K262">
         <v>15.75</v>
@@ -12333,7 +12333,7 @@
         <v>374</v>
       </c>
       <c r="J263">
-        <v>286</v>
+        <v>28600</v>
       </c>
       <c r="K263">
         <v>16.5</v>
@@ -12372,7 +12372,7 @@
         <v>391</v>
       </c>
       <c r="J264">
-        <v>299</v>
+        <v>29900</v>
       </c>
       <c r="K264">
         <v>17.25</v>
@@ -12411,7 +12411,7 @@
         <v>408</v>
       </c>
       <c r="J265">
-        <v>312</v>
+        <v>31200</v>
       </c>
       <c r="K265">
         <v>18</v>
@@ -12450,7 +12450,7 @@
         <v>425</v>
       </c>
       <c r="J266">
-        <v>325</v>
+        <v>32500</v>
       </c>
       <c r="K266">
         <v>18.75</v>
@@ -12489,7 +12489,7 @@
         <v>442</v>
       </c>
       <c r="J267">
-        <v>338</v>
+        <v>33800</v>
       </c>
       <c r="K267">
         <v>19.5</v>
@@ -12528,7 +12528,7 @@
         <v>459</v>
       </c>
       <c r="J268">
-        <v>351</v>
+        <v>35100</v>
       </c>
       <c r="K268">
         <v>20.25</v>
@@ -12567,7 +12567,7 @@
         <v>476</v>
       </c>
       <c r="J269">
-        <v>364</v>
+        <v>36400</v>
       </c>
       <c r="K269">
         <v>21</v>
@@ -12606,7 +12606,7 @@
         <v>493</v>
       </c>
       <c r="J270">
-        <v>377</v>
+        <v>37700</v>
       </c>
       <c r="K270">
         <v>21.75</v>
@@ -12645,7 +12645,7 @@
         <v>510</v>
       </c>
       <c r="J271">
-        <v>390</v>
+        <v>39000</v>
       </c>
       <c r="K271">
         <v>22.5</v>
@@ -12684,7 +12684,7 @@
         <v>527</v>
       </c>
       <c r="J272">
-        <v>403</v>
+        <v>40300</v>
       </c>
       <c r="K272">
         <v>23.25</v>
@@ -12723,7 +12723,7 @@
         <v>544</v>
       </c>
       <c r="J273">
-        <v>416</v>
+        <v>41600</v>
       </c>
       <c r="K273">
         <v>24</v>
@@ -12762,7 +12762,7 @@
         <v>561</v>
       </c>
       <c r="J274">
-        <v>429</v>
+        <v>42900</v>
       </c>
       <c r="K274">
         <v>24.75</v>
@@ -12801,7 +12801,7 @@
         <v>578</v>
       </c>
       <c r="J275">
-        <v>442</v>
+        <v>44200</v>
       </c>
       <c r="K275">
         <v>25.5</v>
@@ -12840,7 +12840,7 @@
         <v>595</v>
       </c>
       <c r="J276">
-        <v>455</v>
+        <v>45500</v>
       </c>
       <c r="K276">
         <v>26.25</v>
@@ -12879,7 +12879,7 @@
         <v>612</v>
       </c>
       <c r="J277">
-        <v>468</v>
+        <v>46800</v>
       </c>
       <c r="K277">
         <v>27</v>
@@ -12918,7 +12918,7 @@
         <v>629</v>
       </c>
       <c r="J278">
-        <v>481</v>
+        <v>48100</v>
       </c>
       <c r="K278">
         <v>27.75</v>
@@ -12957,7 +12957,7 @@
         <v>646</v>
       </c>
       <c r="J279">
-        <v>494</v>
+        <v>49400</v>
       </c>
       <c r="K279">
         <v>28.5</v>
@@ -12996,7 +12996,7 @@
         <v>663</v>
       </c>
       <c r="J280">
-        <v>507</v>
+        <v>50700</v>
       </c>
       <c r="K280">
         <v>29.25</v>
@@ -13035,7 +13035,7 @@
         <v>680</v>
       </c>
       <c r="J281">
-        <v>520</v>
+        <v>52000</v>
       </c>
       <c r="K281">
         <v>30</v>
@@ -13074,7 +13074,7 @@
         <v>697</v>
       </c>
       <c r="J282">
-        <v>533</v>
+        <v>53300</v>
       </c>
       <c r="K282">
         <v>30.75</v>
@@ -13113,7 +13113,7 @@
         <v>714</v>
       </c>
       <c r="J283">
-        <v>546</v>
+        <v>54600</v>
       </c>
       <c r="K283">
         <v>31.5</v>
@@ -13152,7 +13152,7 @@
         <v>731</v>
       </c>
       <c r="J284">
-        <v>559</v>
+        <v>55900</v>
       </c>
       <c r="K284">
         <v>32.25</v>
@@ -13191,7 +13191,7 @@
         <v>748</v>
       </c>
       <c r="J285">
-        <v>572</v>
+        <v>57200</v>
       </c>
       <c r="K285">
         <v>33</v>
@@ -13230,7 +13230,7 @@
         <v>765</v>
       </c>
       <c r="J286">
-        <v>585</v>
+        <v>58500</v>
       </c>
       <c r="K286">
         <v>33.75</v>
@@ -13269,7 +13269,7 @@
         <v>782</v>
       </c>
       <c r="J287">
-        <v>598</v>
+        <v>59800</v>
       </c>
       <c r="K287">
         <v>34.5</v>
@@ -13308,7 +13308,7 @@
         <v>799</v>
       </c>
       <c r="J288">
-        <v>611</v>
+        <v>61100</v>
       </c>
       <c r="K288">
         <v>35.25</v>
@@ -13347,7 +13347,7 @@
         <v>816</v>
       </c>
       <c r="J289">
-        <v>624</v>
+        <v>62400</v>
       </c>
       <c r="K289">
         <v>36</v>
@@ -13386,7 +13386,7 @@
         <v>833</v>
       </c>
       <c r="J290">
-        <v>637</v>
+        <v>63700</v>
       </c>
       <c r="K290">
         <v>36.75</v>
@@ -13425,7 +13425,7 @@
         <v>850</v>
       </c>
       <c r="J291">
-        <v>650</v>
+        <v>65000</v>
       </c>
       <c r="K291">
         <v>37.5</v>
@@ -13464,7 +13464,7 @@
         <v>867</v>
       </c>
       <c r="J292">
-        <v>663</v>
+        <v>66300</v>
       </c>
       <c r="K292">
         <v>38.25</v>
@@ -13503,7 +13503,7 @@
         <v>884</v>
       </c>
       <c r="J293">
-        <v>676</v>
+        <v>67600</v>
       </c>
       <c r="K293">
         <v>39</v>
@@ -13542,7 +13542,7 @@
         <v>901</v>
       </c>
       <c r="J294">
-        <v>689</v>
+        <v>68900</v>
       </c>
       <c r="K294">
         <v>39.75</v>
@@ -13581,7 +13581,7 @@
         <v>918</v>
       </c>
       <c r="J295">
-        <v>702</v>
+        <v>70200</v>
       </c>
       <c r="K295">
         <v>40.5</v>
@@ -13620,7 +13620,7 @@
         <v>935</v>
       </c>
       <c r="J296">
-        <v>715</v>
+        <v>71500</v>
       </c>
       <c r="K296">
         <v>41.25</v>
@@ -13659,7 +13659,7 @@
         <v>952</v>
       </c>
       <c r="J297">
-        <v>728</v>
+        <v>72800</v>
       </c>
       <c r="K297">
         <v>42</v>
@@ -13698,7 +13698,7 @@
         <v>969</v>
       </c>
       <c r="J298">
-        <v>741</v>
+        <v>74100</v>
       </c>
       <c r="K298">
         <v>42.75</v>
@@ -13737,7 +13737,7 @@
         <v>986</v>
       </c>
       <c r="J299">
-        <v>754</v>
+        <v>75400</v>
       </c>
       <c r="K299">
         <v>43.5</v>
@@ -13776,7 +13776,7 @@
         <v>1003</v>
       </c>
       <c r="J300">
-        <v>767</v>
+        <v>76700</v>
       </c>
       <c r="K300">
         <v>44.25</v>
@@ -13815,7 +13815,7 @@
         <v>1020</v>
       </c>
       <c r="J301">
-        <v>780</v>
+        <v>78000</v>
       </c>
       <c r="K301">
         <v>45</v>
@@ -13854,7 +13854,7 @@
         <v>1037</v>
       </c>
       <c r="J302">
-        <v>793</v>
+        <v>79300</v>
       </c>
       <c r="K302">
         <v>45.75</v>
@@ -13893,7 +13893,7 @@
         <v>1054</v>
       </c>
       <c r="J303">
-        <v>806</v>
+        <v>80600</v>
       </c>
       <c r="K303">
         <v>46.5</v>
@@ -13932,7 +13932,7 @@
         <v>1071</v>
       </c>
       <c r="J304">
-        <v>819</v>
+        <v>81900</v>
       </c>
       <c r="K304">
         <v>47.25</v>
@@ -13971,7 +13971,7 @@
         <v>1088</v>
       </c>
       <c r="J305">
-        <v>832</v>
+        <v>83200</v>
       </c>
       <c r="K305">
         <v>48</v>
@@ -14010,7 +14010,7 @@
         <v>1105</v>
       </c>
       <c r="J306">
-        <v>845</v>
+        <v>84500</v>
       </c>
       <c r="K306">
         <v>48.75</v>
@@ -14049,7 +14049,7 @@
         <v>1122</v>
       </c>
       <c r="J307">
-        <v>858</v>
+        <v>85800</v>
       </c>
       <c r="K307">
         <v>49.5</v>
@@ -14088,7 +14088,7 @@
         <v>1139</v>
       </c>
       <c r="J308">
-        <v>871</v>
+        <v>87100</v>
       </c>
       <c r="K308">
         <v>50.25</v>
@@ -14127,7 +14127,7 @@
         <v>1156</v>
       </c>
       <c r="J309">
-        <v>884</v>
+        <v>88400</v>
       </c>
       <c r="K309">
         <v>51</v>
@@ -14166,7 +14166,7 @@
         <v>1173</v>
       </c>
       <c r="J310">
-        <v>897</v>
+        <v>89700</v>
       </c>
       <c r="K310">
         <v>51.75</v>
@@ -14205,7 +14205,7 @@
         <v>1190</v>
       </c>
       <c r="J311">
-        <v>910</v>
+        <v>91000</v>
       </c>
       <c r="K311">
         <v>52.5</v>
@@ -14244,7 +14244,7 @@
         <v>1207</v>
       </c>
       <c r="J312">
-        <v>923</v>
+        <v>92300</v>
       </c>
       <c r="K312">
         <v>53.25</v>
@@ -14283,7 +14283,7 @@
         <v>1224</v>
       </c>
       <c r="J313">
-        <v>936</v>
+        <v>93600</v>
       </c>
       <c r="K313">
         <v>54</v>
@@ -14322,7 +14322,7 @@
         <v>1241</v>
       </c>
       <c r="J314">
-        <v>949</v>
+        <v>94900</v>
       </c>
       <c r="K314">
         <v>54.75</v>
@@ -14361,7 +14361,7 @@
         <v>1258</v>
       </c>
       <c r="J315">
-        <v>962</v>
+        <v>96200</v>
       </c>
       <c r="K315">
         <v>55.5</v>
@@ -14400,7 +14400,7 @@
         <v>1275</v>
       </c>
       <c r="J316">
-        <v>975</v>
+        <v>97500</v>
       </c>
       <c r="K316">
         <v>56.25</v>
@@ -14439,7 +14439,7 @@
         <v>1292</v>
       </c>
       <c r="J317">
-        <v>988</v>
+        <v>98800</v>
       </c>
       <c r="K317">
         <v>57</v>
@@ -14478,7 +14478,7 @@
         <v>1309</v>
       </c>
       <c r="J318">
-        <v>1001</v>
+        <v>100100</v>
       </c>
       <c r="K318">
         <v>57.75</v>
@@ -14517,7 +14517,7 @@
         <v>1326</v>
       </c>
       <c r="J319">
-        <v>1014</v>
+        <v>101400</v>
       </c>
       <c r="K319">
         <v>58.5</v>
@@ -14556,7 +14556,7 @@
         <v>1343</v>
       </c>
       <c r="J320">
-        <v>1027</v>
+        <v>102700</v>
       </c>
       <c r="K320">
         <v>59.25</v>
@@ -14595,7 +14595,7 @@
         <v>1360</v>
       </c>
       <c r="J321">
-        <v>1040</v>
+        <v>104000</v>
       </c>
       <c r="K321">
         <v>60</v>
@@ -14634,7 +14634,7 @@
         <v>1377</v>
       </c>
       <c r="J322">
-        <v>1053</v>
+        <v>105300</v>
       </c>
       <c r="K322">
         <v>60.75</v>
@@ -14673,7 +14673,7 @@
         <v>1394</v>
       </c>
       <c r="J323">
-        <v>1066</v>
+        <v>106600</v>
       </c>
       <c r="K323">
         <v>61.5</v>
@@ -14712,7 +14712,7 @@
         <v>1411</v>
       </c>
       <c r="J324">
-        <v>1079</v>
+        <v>107900</v>
       </c>
       <c r="K324">
         <v>62.25</v>
@@ -14751,7 +14751,7 @@
         <v>1428</v>
       </c>
       <c r="J325">
-        <v>1092</v>
+        <v>109200</v>
       </c>
       <c r="K325">
         <v>63</v>
@@ -14790,7 +14790,7 @@
         <v>1445</v>
       </c>
       <c r="J326">
-        <v>1105</v>
+        <v>110500</v>
       </c>
       <c r="K326">
         <v>63.75</v>
@@ -14829,7 +14829,7 @@
         <v>1462</v>
       </c>
       <c r="J327">
-        <v>1118</v>
+        <v>111800</v>
       </c>
       <c r="K327">
         <v>64.5</v>
@@ -14868,7 +14868,7 @@
         <v>1479</v>
       </c>
       <c r="J328">
-        <v>1131</v>
+        <v>113100</v>
       </c>
       <c r="K328">
         <v>65.25</v>
@@ -14907,7 +14907,7 @@
         <v>1496</v>
       </c>
       <c r="J329">
-        <v>1144</v>
+        <v>114400</v>
       </c>
       <c r="K329">
         <v>66</v>
@@ -14946,7 +14946,7 @@
         <v>1513</v>
       </c>
       <c r="J330">
-        <v>1157</v>
+        <v>115700</v>
       </c>
       <c r="K330">
         <v>66.75</v>
@@ -14985,7 +14985,7 @@
         <v>1530</v>
       </c>
       <c r="J331">
-        <v>1170</v>
+        <v>117000</v>
       </c>
       <c r="K331">
         <v>67.5</v>
@@ -15024,7 +15024,7 @@
         <v>1547</v>
       </c>
       <c r="J332">
-        <v>1183</v>
+        <v>118300</v>
       </c>
       <c r="K332">
         <v>68.25</v>
@@ -15063,7 +15063,7 @@
         <v>1564</v>
       </c>
       <c r="J333">
-        <v>1196</v>
+        <v>119600</v>
       </c>
       <c r="K333">
         <v>69</v>
@@ -15102,7 +15102,7 @@
         <v>1581</v>
       </c>
       <c r="J334">
-        <v>1209</v>
+        <v>120900</v>
       </c>
       <c r="K334">
         <v>69.75</v>
@@ -15141,7 +15141,7 @@
         <v>1598</v>
       </c>
       <c r="J335">
-        <v>1222</v>
+        <v>122200</v>
       </c>
       <c r="K335">
         <v>70.5</v>
@@ -15180,7 +15180,7 @@
         <v>1615</v>
       </c>
       <c r="J336">
-        <v>1235</v>
+        <v>123500</v>
       </c>
       <c r="K336">
         <v>71.25</v>
@@ -15219,7 +15219,7 @@
         <v>1632</v>
       </c>
       <c r="J337">
-        <v>1248</v>
+        <v>124800</v>
       </c>
       <c r="K337">
         <v>72</v>
@@ -15258,7 +15258,7 @@
         <v>1649</v>
       </c>
       <c r="J338">
-        <v>1261</v>
+        <v>126100</v>
       </c>
       <c r="K338">
         <v>72.75</v>
@@ -15297,7 +15297,7 @@
         <v>1666</v>
       </c>
       <c r="J339">
-        <v>1274</v>
+        <v>127400</v>
       </c>
       <c r="K339">
         <v>73.5</v>
@@ -15336,7 +15336,7 @@
         <v>1683</v>
       </c>
       <c r="J340">
-        <v>1287</v>
+        <v>128700</v>
       </c>
       <c r="K340">
         <v>74.25</v>
@@ -15375,7 +15375,7 @@
         <v>1700</v>
       </c>
       <c r="J341">
-        <v>1300</v>
+        <v>130000</v>
       </c>
       <c r="K341">
         <v>75</v>
@@ -15414,7 +15414,7 @@
         <v>1717</v>
       </c>
       <c r="J342">
-        <v>1313</v>
+        <v>131300</v>
       </c>
       <c r="K342">
         <v>75.75</v>
@@ -15453,7 +15453,7 @@
         <v>1734</v>
       </c>
       <c r="J343">
-        <v>1326</v>
+        <v>132600</v>
       </c>
       <c r="K343">
         <v>76.5</v>
@@ -15492,7 +15492,7 @@
         <v>1751</v>
       </c>
       <c r="J344">
-        <v>1339</v>
+        <v>133900</v>
       </c>
       <c r="K344">
         <v>77.25</v>
@@ -15531,7 +15531,7 @@
         <v>1768</v>
       </c>
       <c r="J345">
-        <v>1352</v>
+        <v>135200</v>
       </c>
       <c r="K345">
         <v>78</v>
@@ -15570,7 +15570,7 @@
         <v>1785</v>
       </c>
       <c r="J346">
-        <v>1365</v>
+        <v>136500</v>
       </c>
       <c r="K346">
         <v>78.75</v>
@@ -15609,7 +15609,7 @@
         <v>1802</v>
       </c>
       <c r="J347">
-        <v>1378</v>
+        <v>137800</v>
       </c>
       <c r="K347">
         <v>79.5</v>
@@ -15648,7 +15648,7 @@
         <v>1819</v>
       </c>
       <c r="J348">
-        <v>1391</v>
+        <v>139100</v>
       </c>
       <c r="K348">
         <v>80.25</v>
@@ -15687,7 +15687,7 @@
         <v>1836</v>
       </c>
       <c r="J349">
-        <v>1404</v>
+        <v>140400</v>
       </c>
       <c r="K349">
         <v>81</v>
@@ -15726,7 +15726,7 @@
         <v>1853</v>
       </c>
       <c r="J350">
-        <v>1417</v>
+        <v>141700</v>
       </c>
       <c r="K350">
         <v>81.75</v>
@@ -15765,7 +15765,7 @@
         <v>1870</v>
       </c>
       <c r="J351">
-        <v>1430</v>
+        <v>143000</v>
       </c>
       <c r="K351">
         <v>82.5</v>
@@ -15804,7 +15804,7 @@
         <v>1887</v>
       </c>
       <c r="J352">
-        <v>1443</v>
+        <v>144300</v>
       </c>
       <c r="K352">
         <v>83.25</v>
@@ -15843,7 +15843,7 @@
         <v>1904</v>
       </c>
       <c r="J353">
-        <v>1456</v>
+        <v>145600</v>
       </c>
       <c r="K353">
         <v>84</v>
@@ -15882,7 +15882,7 @@
         <v>1921</v>
       </c>
       <c r="J354">
-        <v>1469</v>
+        <v>146900</v>
       </c>
       <c r="K354">
         <v>84.75</v>
@@ -15921,7 +15921,7 @@
         <v>1938</v>
       </c>
       <c r="J355">
-        <v>1482</v>
+        <v>148200</v>
       </c>
       <c r="K355">
         <v>85.5</v>
@@ -15960,7 +15960,7 @@
         <v>1955</v>
       </c>
       <c r="J356">
-        <v>1495</v>
+        <v>149500</v>
       </c>
       <c r="K356">
         <v>86.25</v>
@@ -15999,7 +15999,7 @@
         <v>1972</v>
       </c>
       <c r="J357">
-        <v>1508</v>
+        <v>150800</v>
       </c>
       <c r="K357">
         <v>87</v>
@@ -16038,7 +16038,7 @@
         <v>1989</v>
       </c>
       <c r="J358">
-        <v>1521</v>
+        <v>152100</v>
       </c>
       <c r="K358">
         <v>87.75</v>
@@ -16077,7 +16077,7 @@
         <v>2006</v>
       </c>
       <c r="J359">
-        <v>1534</v>
+        <v>153400</v>
       </c>
       <c r="K359">
         <v>88.5</v>
@@ -16116,7 +16116,7 @@
         <v>2023</v>
       </c>
       <c r="J360">
-        <v>1547</v>
+        <v>154700</v>
       </c>
       <c r="K360">
         <v>89.25</v>
@@ -16155,7 +16155,7 @@
         <v>2040</v>
       </c>
       <c r="J361">
-        <v>1560</v>
+        <v>156000</v>
       </c>
       <c r="K361">
         <v>90</v>
@@ -16194,7 +16194,7 @@
         <v>25</v>
       </c>
       <c r="J362">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="K362">
         <v>0.75</v>
@@ -16233,7 +16233,7 @@
         <v>50</v>
       </c>
       <c r="J363">
-        <v>36</v>
+        <v>3600</v>
       </c>
       <c r="K363">
         <v>1.5</v>
@@ -16272,7 +16272,7 @@
         <v>75</v>
       </c>
       <c r="J364">
-        <v>54</v>
+        <v>5400</v>
       </c>
       <c r="K364">
         <v>2.25</v>
@@ -16311,7 +16311,7 @@
         <v>100</v>
       </c>
       <c r="J365">
-        <v>72</v>
+        <v>7200</v>
       </c>
       <c r="K365">
         <v>3</v>
@@ -16350,7 +16350,7 @@
         <v>125</v>
       </c>
       <c r="J366">
-        <v>90</v>
+        <v>9000</v>
       </c>
       <c r="K366">
         <v>3.75</v>
@@ -16389,7 +16389,7 @@
         <v>150</v>
       </c>
       <c r="J367">
-        <v>108</v>
+        <v>10800</v>
       </c>
       <c r="K367">
         <v>4.5</v>
@@ -16428,7 +16428,7 @@
         <v>175</v>
       </c>
       <c r="J368">
-        <v>126</v>
+        <v>12600</v>
       </c>
       <c r="K368">
         <v>5.25</v>
@@ -16467,7 +16467,7 @@
         <v>200</v>
       </c>
       <c r="J369">
-        <v>144</v>
+        <v>14400</v>
       </c>
       <c r="K369">
         <v>6</v>
@@ -16506,7 +16506,7 @@
         <v>225</v>
       </c>
       <c r="J370">
-        <v>162</v>
+        <v>16200</v>
       </c>
       <c r="K370">
         <v>6.75</v>
@@ -16545,7 +16545,7 @@
         <v>250</v>
       </c>
       <c r="J371">
-        <v>180</v>
+        <v>18000</v>
       </c>
       <c r="K371">
         <v>7.5</v>
@@ -16584,7 +16584,7 @@
         <v>275</v>
       </c>
       <c r="J372">
-        <v>198</v>
+        <v>19800</v>
       </c>
       <c r="K372">
         <v>8.25</v>
@@ -16623,7 +16623,7 @@
         <v>300</v>
       </c>
       <c r="J373">
-        <v>216</v>
+        <v>21600</v>
       </c>
       <c r="K373">
         <v>9</v>
@@ -16662,7 +16662,7 @@
         <v>325</v>
       </c>
       <c r="J374">
-        <v>234</v>
+        <v>23400</v>
       </c>
       <c r="K374">
         <v>9.75</v>
@@ -16701,7 +16701,7 @@
         <v>350</v>
       </c>
       <c r="J375">
-        <v>252</v>
+        <v>25200</v>
       </c>
       <c r="K375">
         <v>10.5</v>
@@ -16740,7 +16740,7 @@
         <v>375</v>
       </c>
       <c r="J376">
-        <v>270</v>
+        <v>27000</v>
       </c>
       <c r="K376">
         <v>11.25</v>
@@ -16779,7 +16779,7 @@
         <v>400</v>
       </c>
       <c r="J377">
-        <v>288</v>
+        <v>28800</v>
       </c>
       <c r="K377">
         <v>12</v>
@@ -16818,7 +16818,7 @@
         <v>425</v>
       </c>
       <c r="J378">
-        <v>306</v>
+        <v>30600</v>
       </c>
       <c r="K378">
         <v>12.75</v>
@@ -16857,7 +16857,7 @@
         <v>450</v>
       </c>
       <c r="J379">
-        <v>324</v>
+        <v>32400</v>
       </c>
       <c r="K379">
         <v>13.5</v>
@@ -16896,7 +16896,7 @@
         <v>475</v>
       </c>
       <c r="J380">
-        <v>342</v>
+        <v>34200</v>
       </c>
       <c r="K380">
         <v>14.25</v>
@@ -16935,7 +16935,7 @@
         <v>500</v>
       </c>
       <c r="J381">
-        <v>360</v>
+        <v>36000</v>
       </c>
       <c r="K381">
         <v>15</v>
@@ -16974,7 +16974,7 @@
         <v>525</v>
       </c>
       <c r="J382">
-        <v>378</v>
+        <v>37800</v>
       </c>
       <c r="K382">
         <v>15.75</v>
@@ -17013,7 +17013,7 @@
         <v>550</v>
       </c>
       <c r="J383">
-        <v>396</v>
+        <v>39600</v>
       </c>
       <c r="K383">
         <v>16.5</v>
@@ -17052,7 +17052,7 @@
         <v>575</v>
       </c>
       <c r="J384">
-        <v>414</v>
+        <v>41400</v>
       </c>
       <c r="K384">
         <v>17.25</v>
@@ -17091,7 +17091,7 @@
         <v>600</v>
       </c>
       <c r="J385">
-        <v>432</v>
+        <v>43200</v>
       </c>
       <c r="K385">
         <v>18</v>
@@ -17130,7 +17130,7 @@
         <v>625</v>
       </c>
       <c r="J386">
-        <v>450</v>
+        <v>45000</v>
       </c>
       <c r="K386">
         <v>18.75</v>
@@ -17169,7 +17169,7 @@
         <v>650</v>
       </c>
       <c r="J387">
-        <v>468</v>
+        <v>46800</v>
       </c>
       <c r="K387">
         <v>19.5</v>
@@ -17208,7 +17208,7 @@
         <v>675</v>
       </c>
       <c r="J388">
-        <v>486</v>
+        <v>48600</v>
       </c>
       <c r="K388">
         <v>20.25</v>
@@ -17247,7 +17247,7 @@
         <v>700</v>
       </c>
       <c r="J389">
-        <v>504</v>
+        <v>50400</v>
       </c>
       <c r="K389">
         <v>21</v>
@@ -17286,7 +17286,7 @@
         <v>725</v>
       </c>
       <c r="J390">
-        <v>522</v>
+        <v>52200</v>
       </c>
       <c r="K390">
         <v>21.75</v>
@@ -17325,7 +17325,7 @@
         <v>750</v>
       </c>
       <c r="J391">
-        <v>540</v>
+        <v>54000</v>
       </c>
       <c r="K391">
         <v>22.5</v>
@@ -17364,7 +17364,7 @@
         <v>775</v>
       </c>
       <c r="J392">
-        <v>558</v>
+        <v>55800</v>
       </c>
       <c r="K392">
         <v>23.25</v>
@@ -17403,7 +17403,7 @@
         <v>800</v>
       </c>
       <c r="J393">
-        <v>576</v>
+        <v>57600</v>
       </c>
       <c r="K393">
         <v>24</v>
@@ -17442,7 +17442,7 @@
         <v>825</v>
       </c>
       <c r="J394">
-        <v>594</v>
+        <v>59400</v>
       </c>
       <c r="K394">
         <v>24.75</v>
@@ -17481,7 +17481,7 @@
         <v>850</v>
       </c>
       <c r="J395">
-        <v>612</v>
+        <v>61200</v>
       </c>
       <c r="K395">
         <v>25.5</v>
@@ -17520,7 +17520,7 @@
         <v>875</v>
       </c>
       <c r="J396">
-        <v>630</v>
+        <v>63000</v>
       </c>
       <c r="K396">
         <v>26.25</v>
@@ -17559,7 +17559,7 @@
         <v>900</v>
       </c>
       <c r="J397">
-        <v>648</v>
+        <v>64800</v>
       </c>
       <c r="K397">
         <v>27</v>
@@ -17598,7 +17598,7 @@
         <v>925</v>
       </c>
       <c r="J398">
-        <v>666</v>
+        <v>66600</v>
       </c>
       <c r="K398">
         <v>27.75</v>
@@ -17637,7 +17637,7 @@
         <v>950</v>
       </c>
       <c r="J399">
-        <v>684</v>
+        <v>68400</v>
       </c>
       <c r="K399">
         <v>28.5</v>
@@ -17676,7 +17676,7 @@
         <v>975</v>
       </c>
       <c r="J400">
-        <v>702</v>
+        <v>70200</v>
       </c>
       <c r="K400">
         <v>29.25</v>
@@ -17715,7 +17715,7 @@
         <v>1000</v>
       </c>
       <c r="J401">
-        <v>720</v>
+        <v>72000</v>
       </c>
       <c r="K401">
         <v>30</v>
@@ -17754,7 +17754,7 @@
         <v>1025</v>
       </c>
       <c r="J402">
-        <v>738</v>
+        <v>73800</v>
       </c>
       <c r="K402">
         <v>30.75</v>
@@ -17793,7 +17793,7 @@
         <v>1050</v>
       </c>
       <c r="J403">
-        <v>756</v>
+        <v>75600</v>
       </c>
       <c r="K403">
         <v>31.5</v>
@@ -17832,7 +17832,7 @@
         <v>1075</v>
       </c>
       <c r="J404">
-        <v>774</v>
+        <v>77400</v>
       </c>
       <c r="K404">
         <v>32.25</v>
@@ -17871,7 +17871,7 @@
         <v>1100</v>
       </c>
       <c r="J405">
-        <v>792</v>
+        <v>79200</v>
       </c>
       <c r="K405">
         <v>33</v>
@@ -17910,7 +17910,7 @@
         <v>1125</v>
       </c>
       <c r="J406">
-        <v>810</v>
+        <v>81000</v>
       </c>
       <c r="K406">
         <v>33.75</v>
@@ -17949,7 +17949,7 @@
         <v>1150</v>
       </c>
       <c r="J407">
-        <v>828</v>
+        <v>82800</v>
       </c>
       <c r="K407">
         <v>34.5</v>
@@ -17988,7 +17988,7 @@
         <v>1175</v>
       </c>
       <c r="J408">
-        <v>846</v>
+        <v>84600</v>
       </c>
       <c r="K408">
         <v>35.25</v>
@@ -18027,7 +18027,7 @@
         <v>1200</v>
       </c>
       <c r="J409">
-        <v>864</v>
+        <v>86400</v>
       </c>
       <c r="K409">
         <v>36</v>
@@ -18066,7 +18066,7 @@
         <v>1225</v>
       </c>
       <c r="J410">
-        <v>882</v>
+        <v>88200</v>
       </c>
       <c r="K410">
         <v>36.75</v>
@@ -18105,7 +18105,7 @@
         <v>1250</v>
       </c>
       <c r="J411">
-        <v>900</v>
+        <v>90000</v>
       </c>
       <c r="K411">
         <v>37.5</v>
@@ -18144,7 +18144,7 @@
         <v>1275</v>
       </c>
       <c r="J412">
-        <v>918</v>
+        <v>91800</v>
       </c>
       <c r="K412">
         <v>38.25</v>
@@ -18183,7 +18183,7 @@
         <v>1300</v>
       </c>
       <c r="J413">
-        <v>936</v>
+        <v>93600</v>
       </c>
       <c r="K413">
         <v>39</v>
@@ -18222,7 +18222,7 @@
         <v>1325</v>
       </c>
       <c r="J414">
-        <v>954</v>
+        <v>95400</v>
       </c>
       <c r="K414">
         <v>39.75</v>
@@ -18261,7 +18261,7 @@
         <v>1350</v>
       </c>
       <c r="J415">
-        <v>972</v>
+        <v>97200</v>
       </c>
       <c r="K415">
         <v>40.5</v>
@@ -18300,7 +18300,7 @@
         <v>1375</v>
       </c>
       <c r="J416">
-        <v>990</v>
+        <v>99000</v>
       </c>
       <c r="K416">
         <v>41.25</v>
@@ -18339,7 +18339,7 @@
         <v>1400</v>
       </c>
       <c r="J417">
-        <v>1008</v>
+        <v>100800</v>
       </c>
       <c r="K417">
         <v>42</v>
@@ -18378,7 +18378,7 @@
         <v>1425</v>
       </c>
       <c r="J418">
-        <v>1026</v>
+        <v>102600</v>
       </c>
       <c r="K418">
         <v>42.75</v>
@@ -18417,7 +18417,7 @@
         <v>1450</v>
       </c>
       <c r="J419">
-        <v>1044</v>
+        <v>104400</v>
       </c>
       <c r="K419">
         <v>43.5</v>
@@ -18456,7 +18456,7 @@
         <v>1475</v>
       </c>
       <c r="J420">
-        <v>1062</v>
+        <v>106200</v>
       </c>
       <c r="K420">
         <v>44.25</v>
@@ -18495,7 +18495,7 @@
         <v>1500</v>
       </c>
       <c r="J421">
-        <v>1080</v>
+        <v>108000</v>
       </c>
       <c r="K421">
         <v>45</v>
@@ -18534,7 +18534,7 @@
         <v>1525</v>
       </c>
       <c r="J422">
-        <v>1098</v>
+        <v>109800</v>
       </c>
       <c r="K422">
         <v>45.75</v>
@@ -18573,7 +18573,7 @@
         <v>1550</v>
       </c>
       <c r="J423">
-        <v>1116</v>
+        <v>111600</v>
       </c>
       <c r="K423">
         <v>46.5</v>
@@ -18612,7 +18612,7 @@
         <v>1575</v>
       </c>
       <c r="J424">
-        <v>1134</v>
+        <v>113400</v>
       </c>
       <c r="K424">
         <v>47.25</v>
@@ -18651,7 +18651,7 @@
         <v>1600</v>
       </c>
       <c r="J425">
-        <v>1152</v>
+        <v>115200</v>
       </c>
       <c r="K425">
         <v>48</v>
@@ -18690,7 +18690,7 @@
         <v>1625</v>
       </c>
       <c r="J426">
-        <v>1170</v>
+        <v>117000</v>
       </c>
       <c r="K426">
         <v>48.75</v>
@@ -18729,7 +18729,7 @@
         <v>1650</v>
       </c>
       <c r="J427">
-        <v>1188</v>
+        <v>118800</v>
       </c>
       <c r="K427">
         <v>49.5</v>
@@ -18768,7 +18768,7 @@
         <v>1675</v>
       </c>
       <c r="J428">
-        <v>1206</v>
+        <v>120600</v>
       </c>
       <c r="K428">
         <v>50.25</v>
@@ -18807,7 +18807,7 @@
         <v>1700</v>
       </c>
       <c r="J429">
-        <v>1224</v>
+        <v>122400</v>
       </c>
       <c r="K429">
         <v>51</v>
@@ -18846,7 +18846,7 @@
         <v>1725</v>
       </c>
       <c r="J430">
-        <v>1242</v>
+        <v>124200</v>
       </c>
       <c r="K430">
         <v>51.75</v>
@@ -18885,7 +18885,7 @@
         <v>1750</v>
       </c>
       <c r="J431">
-        <v>1260</v>
+        <v>126000</v>
       </c>
       <c r="K431">
         <v>52.5</v>
@@ -18924,7 +18924,7 @@
         <v>1775</v>
       </c>
       <c r="J432">
-        <v>1278</v>
+        <v>127800</v>
       </c>
       <c r="K432">
         <v>53.25</v>
@@ -18963,7 +18963,7 @@
         <v>1800</v>
       </c>
       <c r="J433">
-        <v>1296</v>
+        <v>129600</v>
       </c>
       <c r="K433">
         <v>54</v>
@@ -19002,7 +19002,7 @@
         <v>1825</v>
       </c>
       <c r="J434">
-        <v>1314</v>
+        <v>131400</v>
       </c>
       <c r="K434">
         <v>54.75</v>
@@ -19041,7 +19041,7 @@
         <v>1850</v>
       </c>
       <c r="J435">
-        <v>1332</v>
+        <v>133200</v>
       </c>
       <c r="K435">
         <v>55.5</v>
@@ -19080,7 +19080,7 @@
         <v>1875</v>
       </c>
       <c r="J436">
-        <v>1350</v>
+        <v>135000</v>
       </c>
       <c r="K436">
         <v>56.25</v>
@@ -19119,7 +19119,7 @@
         <v>1900</v>
       </c>
       <c r="J437">
-        <v>1368</v>
+        <v>136800</v>
       </c>
       <c r="K437">
         <v>57</v>
@@ -19158,7 +19158,7 @@
         <v>1925</v>
       </c>
       <c r="J438">
-        <v>1386</v>
+        <v>138600</v>
       </c>
       <c r="K438">
         <v>57.75</v>
@@ -19197,7 +19197,7 @@
         <v>1950</v>
       </c>
       <c r="J439">
-        <v>1404</v>
+        <v>140400</v>
       </c>
       <c r="K439">
         <v>58.5</v>
@@ -19236,7 +19236,7 @@
         <v>1975</v>
       </c>
       <c r="J440">
-        <v>1422</v>
+        <v>142200</v>
       </c>
       <c r="K440">
         <v>59.25</v>
@@ -19275,7 +19275,7 @@
         <v>2000</v>
       </c>
       <c r="J441">
-        <v>1440</v>
+        <v>144000</v>
       </c>
       <c r="K441">
         <v>60</v>
@@ -19314,7 +19314,7 @@
         <v>2025</v>
       </c>
       <c r="J442">
-        <v>1458</v>
+        <v>145800</v>
       </c>
       <c r="K442">
         <v>60.75</v>
@@ -19353,7 +19353,7 @@
         <v>2050</v>
       </c>
       <c r="J443">
-        <v>1476</v>
+        <v>147600</v>
       </c>
       <c r="K443">
         <v>61.5</v>
@@ -19392,7 +19392,7 @@
         <v>2075</v>
       </c>
       <c r="J444">
-        <v>1494</v>
+        <v>149400</v>
       </c>
       <c r="K444">
         <v>62.25</v>
@@ -19431,7 +19431,7 @@
         <v>2100</v>
       </c>
       <c r="J445">
-        <v>1512</v>
+        <v>151200</v>
       </c>
       <c r="K445">
         <v>63</v>
@@ -19470,7 +19470,7 @@
         <v>2125</v>
       </c>
       <c r="J446">
-        <v>1530</v>
+        <v>153000</v>
       </c>
       <c r="K446">
         <v>63.75</v>
@@ -19509,7 +19509,7 @@
         <v>2150</v>
       </c>
       <c r="J447">
-        <v>1548</v>
+        <v>154800</v>
       </c>
       <c r="K447">
         <v>64.5</v>
@@ -19548,7 +19548,7 @@
         <v>2175</v>
       </c>
       <c r="J448">
-        <v>1566</v>
+        <v>156600</v>
       </c>
       <c r="K448">
         <v>65.25</v>
@@ -19587,7 +19587,7 @@
         <v>2200</v>
       </c>
       <c r="J449">
-        <v>1584</v>
+        <v>158400</v>
       </c>
       <c r="K449">
         <v>66</v>
@@ -19626,7 +19626,7 @@
         <v>2225</v>
       </c>
       <c r="J450">
-        <v>1602</v>
+        <v>160200</v>
       </c>
       <c r="K450">
         <v>66.75</v>
@@ -19665,7 +19665,7 @@
         <v>2250</v>
       </c>
       <c r="J451">
-        <v>1620</v>
+        <v>162000</v>
       </c>
       <c r="K451">
         <v>67.5</v>
@@ -19704,7 +19704,7 @@
         <v>2275</v>
       </c>
       <c r="J452">
-        <v>1638</v>
+        <v>163800</v>
       </c>
       <c r="K452">
         <v>68.25</v>
@@ -19743,7 +19743,7 @@
         <v>2300</v>
       </c>
       <c r="J453">
-        <v>1656</v>
+        <v>165600</v>
       </c>
       <c r="K453">
         <v>69</v>
@@ -19782,7 +19782,7 @@
         <v>2325</v>
       </c>
       <c r="J454">
-        <v>1674</v>
+        <v>167400</v>
       </c>
       <c r="K454">
         <v>69.75</v>
@@ -19821,7 +19821,7 @@
         <v>2350</v>
       </c>
       <c r="J455">
-        <v>1692</v>
+        <v>169200</v>
       </c>
       <c r="K455">
         <v>70.5</v>
@@ -19860,7 +19860,7 @@
         <v>2375</v>
       </c>
       <c r="J456">
-        <v>1710</v>
+        <v>171000</v>
       </c>
       <c r="K456">
         <v>71.25</v>
@@ -19899,7 +19899,7 @@
         <v>2400</v>
       </c>
       <c r="J457">
-        <v>1728</v>
+        <v>172800</v>
       </c>
       <c r="K457">
         <v>72</v>
@@ -19938,7 +19938,7 @@
         <v>2425</v>
       </c>
       <c r="J458">
-        <v>1746</v>
+        <v>174600</v>
       </c>
       <c r="K458">
         <v>72.75</v>
@@ -19977,7 +19977,7 @@
         <v>2450</v>
       </c>
       <c r="J459">
-        <v>1764</v>
+        <v>176400</v>
       </c>
       <c r="K459">
         <v>73.5</v>
@@ -20016,7 +20016,7 @@
         <v>2475</v>
       </c>
       <c r="J460">
-        <v>1782</v>
+        <v>178200</v>
       </c>
       <c r="K460">
         <v>74.25</v>
@@ -20055,7 +20055,7 @@
         <v>2500</v>
       </c>
       <c r="J461">
-        <v>1800</v>
+        <v>180000</v>
       </c>
       <c r="K461">
         <v>75</v>
@@ -20094,7 +20094,7 @@
         <v>2525</v>
       </c>
       <c r="J462">
-        <v>1818</v>
+        <v>181800</v>
       </c>
       <c r="K462">
         <v>75.75</v>
@@ -20133,7 +20133,7 @@
         <v>2550</v>
       </c>
       <c r="J463">
-        <v>1836</v>
+        <v>183600</v>
       </c>
       <c r="K463">
         <v>76.5</v>
@@ -20172,7 +20172,7 @@
         <v>2575</v>
       </c>
       <c r="J464">
-        <v>1854</v>
+        <v>185400</v>
       </c>
       <c r="K464">
         <v>77.25</v>
@@ -20211,7 +20211,7 @@
         <v>2600</v>
       </c>
       <c r="J465">
-        <v>1872</v>
+        <v>187200</v>
       </c>
       <c r="K465">
         <v>78</v>
@@ -20250,7 +20250,7 @@
         <v>2625</v>
       </c>
       <c r="J466">
-        <v>1890</v>
+        <v>189000</v>
       </c>
       <c r="K466">
         <v>78.75</v>
@@ -20289,7 +20289,7 @@
         <v>2650</v>
       </c>
       <c r="J467">
-        <v>1908</v>
+        <v>190800</v>
       </c>
       <c r="K467">
         <v>79.5</v>
@@ -20328,7 +20328,7 @@
         <v>2675</v>
       </c>
       <c r="J468">
-        <v>1926</v>
+        <v>192600</v>
       </c>
       <c r="K468">
         <v>80.25</v>
@@ -20367,7 +20367,7 @@
         <v>2700</v>
       </c>
       <c r="J469">
-        <v>1944</v>
+        <v>194400</v>
       </c>
       <c r="K469">
         <v>81</v>
@@ -20406,7 +20406,7 @@
         <v>2725</v>
       </c>
       <c r="J470">
-        <v>1962</v>
+        <v>196200</v>
       </c>
       <c r="K470">
         <v>81.75</v>
@@ -20445,7 +20445,7 @@
         <v>2750</v>
       </c>
       <c r="J471">
-        <v>1980</v>
+        <v>198000</v>
       </c>
       <c r="K471">
         <v>82.5</v>
@@ -20484,7 +20484,7 @@
         <v>2775</v>
       </c>
       <c r="J472">
-        <v>1998</v>
+        <v>199800</v>
       </c>
       <c r="K472">
         <v>83.25</v>
@@ -20523,7 +20523,7 @@
         <v>2800</v>
       </c>
       <c r="J473">
-        <v>2016</v>
+        <v>201600</v>
       </c>
       <c r="K473">
         <v>84</v>
@@ -20562,7 +20562,7 @@
         <v>2825</v>
       </c>
       <c r="J474">
-        <v>2034</v>
+        <v>203400</v>
       </c>
       <c r="K474">
         <v>84.75</v>
@@ -20601,7 +20601,7 @@
         <v>2850</v>
       </c>
       <c r="J475">
-        <v>2052</v>
+        <v>205200</v>
       </c>
       <c r="K475">
         <v>85.5</v>
@@ -20640,7 +20640,7 @@
         <v>2875</v>
       </c>
       <c r="J476">
-        <v>2070</v>
+        <v>207000</v>
       </c>
       <c r="K476">
         <v>86.25</v>
@@ -20679,7 +20679,7 @@
         <v>2900</v>
       </c>
       <c r="J477">
-        <v>2088</v>
+        <v>208800</v>
       </c>
       <c r="K477">
         <v>87</v>
@@ -20718,7 +20718,7 @@
         <v>2925</v>
       </c>
       <c r="J478">
-        <v>2106</v>
+        <v>210600</v>
       </c>
       <c r="K478">
         <v>87.75</v>
@@ -20757,7 +20757,7 @@
         <v>2950</v>
       </c>
       <c r="J479">
-        <v>2124</v>
+        <v>212400</v>
       </c>
       <c r="K479">
         <v>88.5</v>
@@ -20796,7 +20796,7 @@
         <v>2975</v>
       </c>
       <c r="J480">
-        <v>2142</v>
+        <v>214200</v>
       </c>
       <c r="K480">
         <v>89.25</v>
@@ -20835,7 +20835,7 @@
         <v>3000</v>
       </c>
       <c r="J481">
-        <v>2160</v>
+        <v>216000</v>
       </c>
       <c r="K481">
         <v>90</v>
@@ -20874,7 +20874,7 @@
         <v>30</v>
       </c>
       <c r="J482">
-        <v>22</v>
+        <v>2200</v>
       </c>
       <c r="K482">
         <v>0.75</v>
@@ -20913,7 +20913,7 @@
         <v>60</v>
       </c>
       <c r="J483">
-        <v>44</v>
+        <v>4400</v>
       </c>
       <c r="K483">
         <v>1.5</v>
@@ -20952,7 +20952,7 @@
         <v>90</v>
       </c>
       <c r="J484">
-        <v>66</v>
+        <v>6600</v>
       </c>
       <c r="K484">
         <v>2.25</v>
@@ -20991,7 +20991,7 @@
         <v>120</v>
       </c>
       <c r="J485">
-        <v>88</v>
+        <v>8800</v>
       </c>
       <c r="K485">
         <v>3</v>
@@ -21030,7 +21030,7 @@
         <v>150</v>
       </c>
       <c r="J486">
-        <v>110</v>
+        <v>11000</v>
       </c>
       <c r="K486">
         <v>3.75</v>
@@ -21069,7 +21069,7 @@
         <v>180</v>
       </c>
       <c r="J487">
-        <v>132</v>
+        <v>13200</v>
       </c>
       <c r="K487">
         <v>4.5</v>
@@ -21108,7 +21108,7 @@
         <v>210</v>
       </c>
       <c r="J488">
-        <v>154</v>
+        <v>15400</v>
       </c>
       <c r="K488">
         <v>5.25</v>
@@ -21147,7 +21147,7 @@
         <v>240</v>
       </c>
       <c r="J489">
-        <v>176</v>
+        <v>17600</v>
       </c>
       <c r="K489">
         <v>6</v>
@@ -21186,7 +21186,7 @@
         <v>270</v>
       </c>
       <c r="J490">
-        <v>198</v>
+        <v>19800</v>
       </c>
       <c r="K490">
         <v>6.75</v>
@@ -21225,7 +21225,7 @@
         <v>300</v>
       </c>
       <c r="J491">
-        <v>220</v>
+        <v>22000</v>
       </c>
       <c r="K491">
         <v>7.5</v>
@@ -21264,7 +21264,7 @@
         <v>330</v>
       </c>
       <c r="J492">
-        <v>242</v>
+        <v>24200</v>
       </c>
       <c r="K492">
         <v>8.25</v>
@@ -21303,7 +21303,7 @@
         <v>360</v>
       </c>
       <c r="J493">
-        <v>264</v>
+        <v>26400</v>
       </c>
       <c r="K493">
         <v>9</v>
@@ -21342,7 +21342,7 @@
         <v>390</v>
       </c>
       <c r="J494">
-        <v>286</v>
+        <v>28600</v>
       </c>
       <c r="K494">
         <v>9.75</v>
@@ -21381,7 +21381,7 @@
         <v>420</v>
       </c>
       <c r="J495">
-        <v>308</v>
+        <v>30800</v>
       </c>
       <c r="K495">
         <v>10.5</v>
@@ -21420,7 +21420,7 @@
         <v>450</v>
       </c>
       <c r="J496">
-        <v>330</v>
+        <v>33000</v>
       </c>
       <c r="K496">
         <v>11.25</v>
@@ -21459,7 +21459,7 @@
         <v>480</v>
       </c>
       <c r="J497">
-        <v>352</v>
+        <v>35200</v>
       </c>
       <c r="K497">
         <v>12</v>
@@ -21498,7 +21498,7 @@
         <v>510</v>
       </c>
       <c r="J498">
-        <v>374</v>
+        <v>37400</v>
       </c>
       <c r="K498">
         <v>12.75</v>
@@ -21537,7 +21537,7 @@
         <v>540</v>
       </c>
       <c r="J499">
-        <v>396</v>
+        <v>39600</v>
       </c>
       <c r="K499">
         <v>13.5</v>
@@ -21576,7 +21576,7 @@
         <v>570</v>
       </c>
       <c r="J500">
-        <v>418</v>
+        <v>41800</v>
       </c>
       <c r="K500">
         <v>14.25</v>
@@ -21615,7 +21615,7 @@
         <v>600</v>
       </c>
       <c r="J501">
-        <v>440</v>
+        <v>44000</v>
       </c>
       <c r="K501">
         <v>15</v>
@@ -21654,7 +21654,7 @@
         <v>630</v>
       </c>
       <c r="J502">
-        <v>462</v>
+        <v>46200</v>
       </c>
       <c r="K502">
         <v>15.75</v>
@@ -21693,7 +21693,7 @@
         <v>660</v>
       </c>
       <c r="J503">
-        <v>484</v>
+        <v>48400</v>
       </c>
       <c r="K503">
         <v>16.5</v>
@@ -21732,7 +21732,7 @@
         <v>690</v>
       </c>
       <c r="J504">
-        <v>506</v>
+        <v>50600</v>
       </c>
       <c r="K504">
         <v>17.25</v>
@@ -21771,7 +21771,7 @@
         <v>720</v>
       </c>
       <c r="J505">
-        <v>528</v>
+        <v>52800</v>
       </c>
       <c r="K505">
         <v>18</v>
@@ -21810,7 +21810,7 @@
         <v>750</v>
       </c>
       <c r="J506">
-        <v>550</v>
+        <v>55000</v>
       </c>
       <c r="K506">
         <v>18.75</v>
@@ -21849,7 +21849,7 @@
         <v>780</v>
       </c>
       <c r="J507">
-        <v>572</v>
+        <v>57200</v>
       </c>
       <c r="K507">
         <v>19.5</v>
@@ -21888,7 +21888,7 @@
         <v>810</v>
       </c>
       <c r="J508">
-        <v>594</v>
+        <v>59400</v>
       </c>
       <c r="K508">
         <v>20.25</v>
@@ -21927,7 +21927,7 @@
         <v>840</v>
       </c>
       <c r="J509">
-        <v>616</v>
+        <v>61600</v>
       </c>
       <c r="K509">
         <v>21</v>
@@ -21966,7 +21966,7 @@
         <v>870</v>
       </c>
       <c r="J510">
-        <v>638</v>
+        <v>63800</v>
       </c>
       <c r="K510">
         <v>21.75</v>
@@ -22005,7 +22005,7 @@
         <v>900</v>
       </c>
       <c r="J511">
-        <v>660</v>
+        <v>66000</v>
       </c>
       <c r="K511">
         <v>22.5</v>
@@ -22044,7 +22044,7 @@
         <v>930</v>
       </c>
       <c r="J512">
-        <v>682</v>
+        <v>68200</v>
       </c>
       <c r="K512">
         <v>23.25</v>
@@ -22083,7 +22083,7 @@
         <v>960</v>
       </c>
       <c r="J513">
-        <v>704</v>
+        <v>70400</v>
       </c>
       <c r="K513">
         <v>24</v>
@@ -22122,7 +22122,7 @@
         <v>990</v>
       </c>
       <c r="J514">
-        <v>726</v>
+        <v>72600</v>
       </c>
       <c r="K514">
         <v>24.75</v>
@@ -22161,7 +22161,7 @@
         <v>1020</v>
       </c>
       <c r="J515">
-        <v>748</v>
+        <v>74800</v>
       </c>
       <c r="K515">
         <v>25.5</v>
@@ -22200,7 +22200,7 @@
         <v>1050</v>
       </c>
       <c r="J516">
-        <v>770</v>
+        <v>77000</v>
       </c>
       <c r="K516">
         <v>26.25</v>
@@ -22239,7 +22239,7 @@
         <v>1080</v>
       </c>
       <c r="J517">
-        <v>792</v>
+        <v>79200</v>
       </c>
       <c r="K517">
         <v>27</v>
@@ -22278,7 +22278,7 @@
         <v>1110</v>
       </c>
       <c r="J518">
-        <v>814</v>
+        <v>81400</v>
       </c>
       <c r="K518">
         <v>27.75</v>
@@ -22317,7 +22317,7 @@
         <v>1140</v>
       </c>
       <c r="J519">
-        <v>836</v>
+        <v>83600</v>
       </c>
       <c r="K519">
         <v>28.5</v>
@@ -22356,7 +22356,7 @@
         <v>1170</v>
       </c>
       <c r="J520">
-        <v>858</v>
+        <v>85800</v>
       </c>
       <c r="K520">
         <v>29.25</v>
@@ -22395,7 +22395,7 @@
         <v>1200</v>
       </c>
       <c r="J521">
-        <v>880</v>
+        <v>88000</v>
       </c>
       <c r="K521">
         <v>30</v>
@@ -22434,7 +22434,7 @@
         <v>1230</v>
       </c>
       <c r="J522">
-        <v>902</v>
+        <v>90200</v>
       </c>
       <c r="K522">
         <v>30.75</v>
@@ -22473,7 +22473,7 @@
         <v>1260</v>
       </c>
       <c r="J523">
-        <v>924</v>
+        <v>92400</v>
       </c>
       <c r="K523">
         <v>31.5</v>
@@ -22512,7 +22512,7 @@
         <v>1290</v>
       </c>
       <c r="J524">
-        <v>946</v>
+        <v>94600</v>
       </c>
       <c r="K524">
         <v>32.25</v>
@@ -22551,7 +22551,7 @@
         <v>1320</v>
       </c>
       <c r="J525">
-        <v>968</v>
+        <v>96800</v>
       </c>
       <c r="K525">
         <v>33</v>
@@ -22590,7 +22590,7 @@
         <v>1350</v>
       </c>
       <c r="J526">
-        <v>990</v>
+        <v>99000</v>
       </c>
       <c r="K526">
         <v>33.75</v>
@@ -22629,7 +22629,7 @@
         <v>1380</v>
       </c>
       <c r="J527">
-        <v>1012</v>
+        <v>101200</v>
       </c>
       <c r="K527">
         <v>34.5</v>
@@ -22668,7 +22668,7 @@
         <v>1410</v>
       </c>
       <c r="J528">
-        <v>1034</v>
+        <v>103400</v>
       </c>
       <c r="K528">
         <v>35.25</v>
@@ -22707,7 +22707,7 @@
         <v>1440</v>
       </c>
       <c r="J529">
-        <v>1056</v>
+        <v>105600</v>
       </c>
       <c r="K529">
         <v>36</v>
@@ -22746,7 +22746,7 @@
         <v>1470</v>
       </c>
       <c r="J530">
-        <v>1078</v>
+        <v>107800</v>
       </c>
       <c r="K530">
         <v>36.75</v>
@@ -22785,7 +22785,7 @@
         <v>1500</v>
       </c>
       <c r="J531">
-        <v>1100</v>
+        <v>110000</v>
       </c>
       <c r="K531">
         <v>37.5</v>
@@ -22824,7 +22824,7 @@
         <v>1530</v>
       </c>
       <c r="J532">
-        <v>1122</v>
+        <v>112200</v>
       </c>
       <c r="K532">
         <v>38.25</v>
@@ -22863,7 +22863,7 @@
         <v>1560</v>
       </c>
       <c r="J533">
-        <v>1144</v>
+        <v>114400</v>
       </c>
       <c r="K533">
         <v>39</v>
@@ -22902,7 +22902,7 @@
         <v>1590</v>
       </c>
       <c r="J534">
-        <v>1166</v>
+        <v>116600</v>
       </c>
       <c r="K534">
         <v>39.75</v>
@@ -22941,7 +22941,7 @@
         <v>1620</v>
       </c>
       <c r="J535">
-        <v>1188</v>
+        <v>118800</v>
       </c>
       <c r="K535">
         <v>40.5</v>
@@ -22980,7 +22980,7 @@
         <v>1650</v>
       </c>
       <c r="J536">
-        <v>1210</v>
+        <v>121000</v>
       </c>
       <c r="K536">
         <v>41.25</v>
@@ -23019,7 +23019,7 @@
         <v>1680</v>
       </c>
       <c r="J537">
-        <v>1232</v>
+        <v>123200</v>
       </c>
       <c r="K537">
         <v>42</v>
@@ -23058,7 +23058,7 @@
         <v>1710</v>
       </c>
       <c r="J538">
-        <v>1254</v>
+        <v>125400</v>
       </c>
       <c r="K538">
         <v>42.75</v>
@@ -23097,7 +23097,7 @@
         <v>1740</v>
       </c>
       <c r="J539">
-        <v>1276</v>
+        <v>127600</v>
       </c>
       <c r="K539">
         <v>43.5</v>
@@ -23136,7 +23136,7 @@
         <v>1770</v>
       </c>
       <c r="J540">
-        <v>1298</v>
+        <v>129800</v>
       </c>
       <c r="K540">
         <v>44.25</v>
@@ -23175,7 +23175,7 @@
         <v>1800</v>
       </c>
       <c r="J541">
-        <v>1320</v>
+        <v>132000</v>
       </c>
       <c r="K541">
         <v>45</v>
@@ -23214,7 +23214,7 @@
         <v>1830</v>
       </c>
       <c r="J542">
-        <v>1342</v>
+        <v>134200</v>
       </c>
       <c r="K542">
         <v>45.75</v>
@@ -23253,7 +23253,7 @@
         <v>1860</v>
       </c>
       <c r="J543">
-        <v>1364</v>
+        <v>136400</v>
       </c>
       <c r="K543">
         <v>46.5</v>
@@ -23292,7 +23292,7 @@
         <v>1890</v>
       </c>
       <c r="J544">
-        <v>1386</v>
+        <v>138600</v>
       </c>
       <c r="K544">
         <v>47.25</v>
@@ -23331,7 +23331,7 @@
         <v>1920</v>
       </c>
       <c r="J545">
-        <v>1408</v>
+        <v>140800</v>
       </c>
       <c r="K545">
         <v>48</v>
@@ -23370,7 +23370,7 @@
         <v>1950</v>
       </c>
       <c r="J546">
-        <v>1430</v>
+        <v>143000</v>
       </c>
       <c r="K546">
         <v>48.75</v>
@@ -23409,7 +23409,7 @@
         <v>1980</v>
       </c>
       <c r="J547">
-        <v>1452</v>
+        <v>145200</v>
       </c>
       <c r="K547">
         <v>49.5</v>
@@ -23448,7 +23448,7 @@
         <v>2010</v>
       </c>
       <c r="J548">
-        <v>1474</v>
+        <v>147400</v>
       </c>
       <c r="K548">
         <v>50.25</v>
@@ -23487,7 +23487,7 @@
         <v>2040</v>
       </c>
       <c r="J549">
-        <v>1496</v>
+        <v>149600</v>
       </c>
       <c r="K549">
         <v>51</v>
@@ -23526,7 +23526,7 @@
         <v>2070</v>
       </c>
       <c r="J550">
-        <v>1518</v>
+        <v>151800</v>
       </c>
       <c r="K550">
         <v>51.75</v>
@@ -23565,7 +23565,7 @@
         <v>2100</v>
       </c>
       <c r="J551">
-        <v>1540</v>
+        <v>154000</v>
       </c>
       <c r="K551">
         <v>52.5</v>
@@ -23604,7 +23604,7 @@
         <v>2130</v>
       </c>
       <c r="J552">
-        <v>1562</v>
+        <v>156200</v>
       </c>
       <c r="K552">
         <v>53.25</v>
@@ -23643,7 +23643,7 @@
         <v>2160</v>
       </c>
       <c r="J553">
-        <v>1584</v>
+        <v>158400</v>
       </c>
       <c r="K553">
         <v>54</v>
@@ -23682,7 +23682,7 @@
         <v>2190</v>
       </c>
       <c r="J554">
-        <v>1606</v>
+        <v>160600</v>
       </c>
       <c r="K554">
         <v>54.75</v>
@@ -23721,7 +23721,7 @@
         <v>2220</v>
       </c>
       <c r="J555">
-        <v>1628</v>
+        <v>162800</v>
       </c>
       <c r="K555">
         <v>55.5</v>
@@ -23760,7 +23760,7 @@
         <v>2250</v>
       </c>
       <c r="J556">
-        <v>1650</v>
+        <v>165000</v>
       </c>
       <c r="K556">
         <v>56.25</v>
@@ -23799,7 +23799,7 @@
         <v>2280</v>
       </c>
       <c r="J557">
-        <v>1672</v>
+        <v>167200</v>
       </c>
       <c r="K557">
         <v>57</v>
@@ -23838,7 +23838,7 @@
         <v>2310</v>
       </c>
       <c r="J558">
-        <v>1694</v>
+        <v>169400</v>
       </c>
       <c r="K558">
         <v>57.75</v>
@@ -23877,7 +23877,7 @@
         <v>2340</v>
       </c>
       <c r="J559">
-        <v>1716</v>
+        <v>171600</v>
       </c>
       <c r="K559">
         <v>58.5</v>
@@ -23916,7 +23916,7 @@
         <v>2370</v>
       </c>
       <c r="J560">
-        <v>1738</v>
+        <v>173800</v>
       </c>
       <c r="K560">
         <v>59.25</v>
@@ -23955,7 +23955,7 @@
         <v>2400</v>
       </c>
       <c r="J561">
-        <v>1760</v>
+        <v>176000</v>
       </c>
       <c r="K561">
         <v>60</v>
@@ -23994,7 +23994,7 @@
         <v>2430</v>
       </c>
       <c r="J562">
-        <v>1782</v>
+        <v>178200</v>
       </c>
       <c r="K562">
         <v>60.75</v>
@@ -24033,7 +24033,7 @@
         <v>2460</v>
       </c>
       <c r="J563">
-        <v>1804</v>
+        <v>180400</v>
       </c>
       <c r="K563">
         <v>61.5</v>
@@ -24072,7 +24072,7 @@
         <v>2490</v>
       </c>
       <c r="J564">
-        <v>1826</v>
+        <v>182600</v>
       </c>
       <c r="K564">
         <v>62.25</v>
@@ -24111,7 +24111,7 @@
         <v>2520</v>
       </c>
       <c r="J565">
-        <v>1848</v>
+        <v>184800</v>
       </c>
       <c r="K565">
         <v>63</v>
@@ -24150,7 +24150,7 @@
         <v>2550</v>
       </c>
       <c r="J566">
-        <v>1870</v>
+        <v>187000</v>
       </c>
       <c r="K566">
         <v>63.75</v>
@@ -24189,7 +24189,7 @@
         <v>2580</v>
       </c>
       <c r="J567">
-        <v>1892</v>
+        <v>189200</v>
       </c>
       <c r="K567">
         <v>64.5</v>
@@ -24228,7 +24228,7 @@
         <v>2610</v>
       </c>
       <c r="J568">
-        <v>1914</v>
+        <v>191400</v>
       </c>
       <c r="K568">
         <v>65.25</v>
@@ -24267,7 +24267,7 @@
         <v>2640</v>
       </c>
       <c r="J569">
-        <v>1936</v>
+        <v>193600</v>
       </c>
       <c r="K569">
         <v>66</v>
@@ -24306,7 +24306,7 @@
         <v>2670</v>
       </c>
       <c r="J570">
-        <v>1958</v>
+        <v>195800</v>
       </c>
       <c r="K570">
         <v>66.75</v>
@@ -24345,7 +24345,7 @@
         <v>2700</v>
       </c>
       <c r="J571">
-        <v>1980</v>
+        <v>198000</v>
       </c>
       <c r="K571">
         <v>67.5</v>
@@ -24384,7 +24384,7 @@
         <v>2730</v>
       </c>
       <c r="J572">
-        <v>2002</v>
+        <v>200200</v>
       </c>
       <c r="K572">
         <v>68.25</v>
@@ -24423,7 +24423,7 @@
         <v>2760</v>
       </c>
       <c r="J573">
-        <v>2024</v>
+        <v>202400</v>
       </c>
       <c r="K573">
         <v>69</v>
@@ -24462,7 +24462,7 @@
         <v>2790</v>
       </c>
       <c r="J574">
-        <v>2046</v>
+        <v>204600</v>
       </c>
       <c r="K574">
         <v>69.75</v>
@@ -24501,7 +24501,7 @@
         <v>2820</v>
       </c>
       <c r="J575">
-        <v>2068</v>
+        <v>206800</v>
       </c>
       <c r="K575">
         <v>70.5</v>
@@ -24540,7 +24540,7 @@
         <v>2850</v>
       </c>
       <c r="J576">
-        <v>2090</v>
+        <v>209000</v>
       </c>
       <c r="K576">
         <v>71.25</v>
@@ -24579,7 +24579,7 @@
         <v>2880</v>
       </c>
       <c r="J577">
-        <v>2112</v>
+        <v>211200</v>
       </c>
       <c r="K577">
         <v>72</v>
@@ -24618,7 +24618,7 @@
         <v>2910</v>
       </c>
       <c r="J578">
-        <v>2134</v>
+        <v>213400</v>
       </c>
       <c r="K578">
         <v>72.75</v>
@@ -24657,7 +24657,7 @@
         <v>2940</v>
       </c>
       <c r="J579">
-        <v>2156</v>
+        <v>215600</v>
       </c>
       <c r="K579">
         <v>73.5</v>
@@ -24696,7 +24696,7 @@
         <v>2970</v>
       </c>
       <c r="J580">
-        <v>2178</v>
+        <v>217800</v>
       </c>
       <c r="K580">
         <v>74.25</v>
@@ -24735,7 +24735,7 @@
         <v>3000</v>
       </c>
       <c r="J581">
-        <v>2200</v>
+        <v>220000</v>
       </c>
       <c r="K581">
         <v>75</v>
@@ -24774,7 +24774,7 @@
         <v>3030</v>
       </c>
       <c r="J582">
-        <v>2222</v>
+        <v>222200</v>
       </c>
       <c r="K582">
         <v>75.75</v>
@@ -24813,7 +24813,7 @@
         <v>3060</v>
       </c>
       <c r="J583">
-        <v>2244</v>
+        <v>224400</v>
       </c>
       <c r="K583">
         <v>76.5</v>
@@ -24852,7 +24852,7 @@
         <v>3090</v>
       </c>
       <c r="J584">
-        <v>2266</v>
+        <v>226600</v>
       </c>
       <c r="K584">
         <v>77.25</v>
@@ -24891,7 +24891,7 @@
         <v>3120</v>
       </c>
       <c r="J585">
-        <v>2288</v>
+        <v>228800</v>
       </c>
       <c r="K585">
         <v>78</v>
@@ -24930,7 +24930,7 @@
         <v>3150</v>
       </c>
       <c r="J586">
-        <v>2310</v>
+        <v>231000</v>
       </c>
       <c r="K586">
         <v>78.75</v>
@@ -24969,7 +24969,7 @@
         <v>3180</v>
       </c>
       <c r="J587">
-        <v>2332</v>
+        <v>233200</v>
       </c>
       <c r="K587">
         <v>79.5</v>
@@ -25008,7 +25008,7 @@
         <v>3210</v>
       </c>
       <c r="J588">
-        <v>2354</v>
+        <v>235400</v>
       </c>
       <c r="K588">
         <v>80.25</v>
@@ -25047,7 +25047,7 @@
         <v>3240</v>
       </c>
       <c r="J589">
-        <v>2376</v>
+        <v>237600</v>
       </c>
       <c r="K589">
         <v>81</v>
@@ -25086,7 +25086,7 @@
         <v>3270</v>
       </c>
       <c r="J590">
-        <v>2398</v>
+        <v>239800</v>
       </c>
       <c r="K590">
         <v>81.75</v>
@@ -25125,7 +25125,7 @@
         <v>3300</v>
       </c>
       <c r="J591">
-        <v>2420</v>
+        <v>242000</v>
       </c>
       <c r="K591">
         <v>82.5</v>
@@ -25164,7 +25164,7 @@
         <v>3330</v>
       </c>
       <c r="J592">
-        <v>2442</v>
+        <v>244200</v>
       </c>
       <c r="K592">
         <v>83.25</v>
@@ -25203,7 +25203,7 @@
         <v>3360</v>
       </c>
       <c r="J593">
-        <v>2464</v>
+        <v>246400</v>
       </c>
       <c r="K593">
         <v>84</v>
@@ -25242,7 +25242,7 @@
         <v>3390</v>
       </c>
       <c r="J594">
-        <v>2486</v>
+        <v>248600</v>
       </c>
       <c r="K594">
         <v>84.75</v>
@@ -25281,7 +25281,7 @@
         <v>3420</v>
       </c>
       <c r="J595">
-        <v>2508</v>
+        <v>250800</v>
       </c>
       <c r="K595">
         <v>85.5</v>
@@ -25320,7 +25320,7 @@
         <v>3450</v>
       </c>
       <c r="J596">
-        <v>2530</v>
+        <v>253000</v>
       </c>
       <c r="K596">
         <v>86.25</v>
@@ -25359,7 +25359,7 @@
         <v>3480</v>
       </c>
       <c r="J597">
-        <v>2552</v>
+        <v>255200</v>
       </c>
       <c r="K597">
         <v>87</v>
@@ -25398,7 +25398,7 @@
         <v>3510</v>
       </c>
       <c r="J598">
-        <v>2574</v>
+        <v>257400</v>
       </c>
       <c r="K598">
         <v>87.75</v>
@@ -25437,7 +25437,7 @@
         <v>3540</v>
       </c>
       <c r="J599">
-        <v>2596</v>
+        <v>259600</v>
       </c>
       <c r="K599">
         <v>88.5</v>
@@ -25476,7 +25476,7 @@
         <v>3570</v>
       </c>
       <c r="J600">
-        <v>2618</v>
+        <v>261800</v>
       </c>
       <c r="K600">
         <v>89.25</v>
@@ -25515,7 +25515,7 @@
         <v>3600</v>
       </c>
       <c r="J601">
-        <v>2640</v>
+        <v>264000</v>
       </c>
       <c r="K601">
         <v>90</v>
@@ -27894,7 +27894,7 @@
         <v>20.15</v>
       </c>
       <c r="J662">
-        <v>17.05</v>
+        <v>1705</v>
       </c>
       <c r="K662">
         <v>0.25</v>
@@ -27933,7 +27933,7 @@
         <v>40.3</v>
       </c>
       <c r="J663">
-        <v>34.1</v>
+        <v>3410</v>
       </c>
       <c r="K663">
         <v>0.5</v>
@@ -27972,7 +27972,7 @@
         <v>60.45</v>
       </c>
       <c r="J664">
-        <v>51.15</v>
+        <v>5115</v>
       </c>
       <c r="K664">
         <v>0.75</v>
@@ -28011,7 +28011,7 @@
         <v>80.6</v>
       </c>
       <c r="J665">
-        <v>68.2</v>
+        <v>6820</v>
       </c>
       <c r="K665">
         <v>1</v>
@@ -28050,7 +28050,7 @@
         <v>100.75</v>
       </c>
       <c r="J666">
-        <v>85.25</v>
+        <v>8525</v>
       </c>
       <c r="K666">
         <v>1.25</v>
@@ -28089,7 +28089,7 @@
         <v>120.9</v>
       </c>
       <c r="J667">
-        <v>102.3</v>
+        <v>10230</v>
       </c>
       <c r="K667">
         <v>1.5</v>
@@ -28128,7 +28128,7 @@
         <v>141.05</v>
       </c>
       <c r="J668">
-        <v>119.35</v>
+        <v>11935</v>
       </c>
       <c r="K668">
         <v>1.75</v>
@@ -28167,7 +28167,7 @@
         <v>161.2</v>
       </c>
       <c r="J669">
-        <v>136.4</v>
+        <v>13640</v>
       </c>
       <c r="K669">
         <v>2</v>
@@ -28206,7 +28206,7 @@
         <v>181.35</v>
       </c>
       <c r="J670">
-        <v>153.45</v>
+        <v>15345</v>
       </c>
       <c r="K670">
         <v>2.25</v>
@@ -28245,7 +28245,7 @@
         <v>201.5</v>
       </c>
       <c r="J671">
-        <v>170.5</v>
+        <v>17050</v>
       </c>
       <c r="K671">
         <v>2.5</v>
@@ -28284,7 +28284,7 @@
         <v>221.65</v>
       </c>
       <c r="J672">
-        <v>187.55</v>
+        <v>18755</v>
       </c>
       <c r="K672">
         <v>2.75</v>
@@ -28323,7 +28323,7 @@
         <v>241.8</v>
       </c>
       <c r="J673">
-        <v>204.6</v>
+        <v>20460</v>
       </c>
       <c r="K673">
         <v>3</v>
@@ -28362,7 +28362,7 @@
         <v>261.95</v>
       </c>
       <c r="J674">
-        <v>221.65</v>
+        <v>22165</v>
       </c>
       <c r="K674">
         <v>3.25</v>
@@ -28401,7 +28401,7 @@
         <v>282.1</v>
       </c>
       <c r="J675">
-        <v>238.7</v>
+        <v>23870</v>
       </c>
       <c r="K675">
         <v>3.5</v>
@@ -28440,7 +28440,7 @@
         <v>302.25</v>
       </c>
       <c r="J676">
-        <v>255.75</v>
+        <v>25575</v>
       </c>
       <c r="K676">
         <v>3.75</v>
@@ -28479,7 +28479,7 @@
         <v>322.4</v>
       </c>
       <c r="J677">
-        <v>272.8</v>
+        <v>27280</v>
       </c>
       <c r="K677">
         <v>4</v>
@@ -28518,7 +28518,7 @@
         <v>342.55</v>
       </c>
       <c r="J678">
-        <v>289.85</v>
+        <v>28985</v>
       </c>
       <c r="K678">
         <v>4.25</v>
@@ -28557,7 +28557,7 @@
         <v>362.7</v>
       </c>
       <c r="J679">
-        <v>306.9</v>
+        <v>30690</v>
       </c>
       <c r="K679">
         <v>4.5</v>
@@ -28596,7 +28596,7 @@
         <v>382.85</v>
       </c>
       <c r="J680">
-        <v>323.95</v>
+        <v>32395</v>
       </c>
       <c r="K680">
         <v>4.75</v>
@@ -28635,7 +28635,7 @@
         <v>403</v>
       </c>
       <c r="J681">
-        <v>341</v>
+        <v>34100</v>
       </c>
       <c r="K681">
         <v>5</v>
@@ -28674,7 +28674,7 @@
         <v>423.15</v>
       </c>
       <c r="J682">
-        <v>358.05</v>
+        <v>35805</v>
       </c>
       <c r="K682">
         <v>5.25</v>
@@ -28713,7 +28713,7 @@
         <v>443.3</v>
       </c>
       <c r="J683">
-        <v>375.1</v>
+        <v>37510</v>
       </c>
       <c r="K683">
         <v>5.5</v>
@@ -28752,7 +28752,7 @@
         <v>463.45</v>
       </c>
       <c r="J684">
-        <v>392.15</v>
+        <v>39215</v>
       </c>
       <c r="K684">
         <v>5.75</v>
@@ -28791,7 +28791,7 @@
         <v>483.6</v>
       </c>
       <c r="J685">
-        <v>409.2</v>
+        <v>40920</v>
       </c>
       <c r="K685">
         <v>6</v>
@@ -28830,7 +28830,7 @@
         <v>503.75</v>
       </c>
       <c r="J686">
-        <v>426.25</v>
+        <v>42625</v>
       </c>
       <c r="K686">
         <v>6.25</v>
@@ -28869,7 +28869,7 @@
         <v>523.9</v>
       </c>
       <c r="J687">
-        <v>443.3</v>
+        <v>44330</v>
       </c>
       <c r="K687">
         <v>6.5</v>
@@ -28908,7 +28908,7 @@
         <v>544.05</v>
       </c>
       <c r="J688">
-        <v>460.35</v>
+        <v>46035</v>
       </c>
       <c r="K688">
         <v>6.75</v>
@@ -28947,7 +28947,7 @@
         <v>564.2</v>
       </c>
       <c r="J689">
-        <v>477.4</v>
+        <v>47740</v>
       </c>
       <c r="K689">
         <v>7</v>
@@ -28986,7 +28986,7 @@
         <v>584.35</v>
       </c>
       <c r="J690">
-        <v>494.45</v>
+        <v>49445</v>
       </c>
       <c r="K690">
         <v>7.25</v>
@@ -29025,7 +29025,7 @@
         <v>604.5</v>
       </c>
       <c r="J691">
-        <v>511.5</v>
+        <v>51150</v>
       </c>
       <c r="K691">
         <v>7.5</v>
@@ -29064,7 +29064,7 @@
         <v>624.65</v>
       </c>
       <c r="J692">
-        <v>528.55</v>
+        <v>52855</v>
       </c>
       <c r="K692">
         <v>7.75</v>
@@ -29103,7 +29103,7 @@
         <v>644.8</v>
       </c>
       <c r="J693">
-        <v>545.6</v>
+        <v>54560</v>
       </c>
       <c r="K693">
         <v>8</v>
@@ -29142,7 +29142,7 @@
         <v>664.95</v>
       </c>
       <c r="J694">
-        <v>562.65</v>
+        <v>56265</v>
       </c>
       <c r="K694">
         <v>8.25</v>
@@ -29181,7 +29181,7 @@
         <v>685.1</v>
       </c>
       <c r="J695">
-        <v>579.7</v>
+        <v>57970</v>
       </c>
       <c r="K695">
         <v>8.5</v>
@@ -29220,7 +29220,7 @@
         <v>705.25</v>
       </c>
       <c r="J696">
-        <v>596.75</v>
+        <v>59675</v>
       </c>
       <c r="K696">
         <v>8.75</v>
@@ -29259,7 +29259,7 @@
         <v>725.4</v>
       </c>
       <c r="J697">
-        <v>613.8</v>
+        <v>61380</v>
       </c>
       <c r="K697">
         <v>9</v>
@@ -29298,7 +29298,7 @@
         <v>745.55</v>
       </c>
       <c r="J698">
-        <v>630.85</v>
+        <v>63085</v>
       </c>
       <c r="K698">
         <v>9.25</v>
@@ -29337,7 +29337,7 @@
         <v>765.7</v>
       </c>
       <c r="J699">
-        <v>647.9</v>
+        <v>64790</v>
       </c>
       <c r="K699">
         <v>9.5</v>
@@ -29376,7 +29376,7 @@
         <v>785.85</v>
       </c>
       <c r="J700">
-        <v>664.95</v>
+        <v>66495</v>
       </c>
       <c r="K700">
         <v>9.75</v>
@@ -29415,7 +29415,7 @@
         <v>806</v>
       </c>
       <c r="J701">
-        <v>682</v>
+        <v>68200</v>
       </c>
       <c r="K701">
         <v>10</v>
@@ -29454,7 +29454,7 @@
         <v>826.15</v>
       </c>
       <c r="J702">
-        <v>699.05</v>
+        <v>69905</v>
       </c>
       <c r="K702">
         <v>10.25</v>
@@ -29493,7 +29493,7 @@
         <v>846.3</v>
       </c>
       <c r="J703">
-        <v>716.1</v>
+        <v>71610</v>
       </c>
       <c r="K703">
         <v>10.5</v>
@@ -29532,7 +29532,7 @@
         <v>866.45</v>
       </c>
       <c r="J704">
-        <v>733.15</v>
+        <v>73315</v>
       </c>
       <c r="K704">
         <v>10.75</v>
@@ -29571,7 +29571,7 @@
         <v>886.6</v>
       </c>
       <c r="J705">
-        <v>750.2</v>
+        <v>75020</v>
       </c>
       <c r="K705">
         <v>11</v>
@@ -29610,7 +29610,7 @@
         <v>906.75</v>
       </c>
       <c r="J706">
-        <v>767.25</v>
+        <v>76725</v>
       </c>
       <c r="K706">
         <v>11.25</v>
@@ -29649,7 +29649,7 @@
         <v>926.9</v>
       </c>
       <c r="J707">
-        <v>784.3</v>
+        <v>78430</v>
       </c>
       <c r="K707">
         <v>11.5</v>
@@ -29688,7 +29688,7 @@
         <v>947.05</v>
       </c>
       <c r="J708">
-        <v>801.35</v>
+        <v>80135</v>
       </c>
       <c r="K708">
         <v>11.75</v>
@@ -29727,7 +29727,7 @@
         <v>967.2</v>
       </c>
       <c r="J709">
-        <v>818.4</v>
+        <v>81840</v>
       </c>
       <c r="K709">
         <v>12</v>
@@ -29766,7 +29766,7 @@
         <v>987.35</v>
       </c>
       <c r="J710">
-        <v>835.45</v>
+        <v>83545</v>
       </c>
       <c r="K710">
         <v>12.25</v>
@@ -29805,7 +29805,7 @@
         <v>1007.5</v>
       </c>
       <c r="J711">
-        <v>852.5</v>
+        <v>85250</v>
       </c>
       <c r="K711">
         <v>12.5</v>
@@ -29844,7 +29844,7 @@
         <v>1027.65</v>
       </c>
       <c r="J712">
-        <v>869.55</v>
+        <v>86955</v>
       </c>
       <c r="K712">
         <v>12.75</v>
@@ -29883,7 +29883,7 @@
         <v>1047.8</v>
       </c>
       <c r="J713">
-        <v>886.6</v>
+        <v>88660</v>
       </c>
       <c r="K713">
         <v>13</v>
@@ -29922,7 +29922,7 @@
         <v>1067.95</v>
       </c>
       <c r="J714">
-        <v>903.65</v>
+        <v>90365</v>
       </c>
       <c r="K714">
         <v>13.25</v>
@@ -29961,7 +29961,7 @@
         <v>1088.1</v>
       </c>
       <c r="J715">
-        <v>920.7</v>
+        <v>92070</v>
       </c>
       <c r="K715">
         <v>13.5</v>
@@ -30000,7 +30000,7 @@
         <v>1108.25</v>
       </c>
       <c r="J716">
-        <v>937.75</v>
+        <v>93775</v>
       </c>
       <c r="K716">
         <v>13.75</v>
@@ -30039,7 +30039,7 @@
         <v>1128.4</v>
       </c>
       <c r="J717">
-        <v>954.8</v>
+        <v>95480</v>
       </c>
       <c r="K717">
         <v>14</v>
@@ -30078,7 +30078,7 @@
         <v>1148.55</v>
       </c>
       <c r="J718">
-        <v>971.85</v>
+        <v>97185</v>
       </c>
       <c r="K718">
         <v>14.25</v>
@@ -30117,7 +30117,7 @@
         <v>1168.7</v>
       </c>
       <c r="J719">
-        <v>988.9</v>
+        <v>98890</v>
       </c>
       <c r="K719">
         <v>14.5</v>
@@ -30156,7 +30156,7 @@
         <v>1188.85</v>
       </c>
       <c r="J720">
-        <v>1005.95</v>
+        <v>100595</v>
       </c>
       <c r="K720">
         <v>14.75</v>
@@ -30195,7 +30195,7 @@
         <v>1209</v>
       </c>
       <c r="J721">
-        <v>1023</v>
+        <v>102300</v>
       </c>
       <c r="K721">
         <v>15</v>
